--- a/analysis/EUS_full_analysis.xlsx
+++ b/analysis/EUS_full_analysis.xlsx
@@ -16,8 +16,9 @@
     <sheet name="Cost category - supercritical" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Cost category - liquid" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Booster reason" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Insulation volume" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Booster vs insulation" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Pipe volume" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Insulation volume" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Booster vs insulation" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2888,6 +2889,927 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Pipeline volume by scenario (no insulation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Installed pipes</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Total pipe length [km]</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Total pipe volume [m³]</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="n"/>
+      <c r="G2" s="11" t="n"/>
+      <c r="H2" s="11" t="n"/>
+      <c r="I2" s="11" t="n"/>
+      <c r="J2" s="11" t="n"/>
+      <c r="K2" s="11" t="n"/>
+      <c r="L2" s="11" t="n"/>
+      <c r="M2" s="11" t="n"/>
+      <c r="N2" s="11" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>bm_dense_2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>benchmark (dense-phase network)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2445.26</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1217041.277013681</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>bm_sco2</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>benchmark (sCO2 network)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2997.59</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1157784.087114436</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ins100</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2659.17</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1535782.637299985</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>3311.17</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1449141.333498078</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ins20</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2394.66</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1150865.685609531</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ins40</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2574.13</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1212340.308510503</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ins60</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3035.1</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1233498.487349194</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ins80</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2560.89</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1204397.486360958</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins20</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>2422.78</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1158939.359898479</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins40</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2394.66</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1201871.914407041</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins60</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2540.54</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1211140.769761086</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2445.26</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1266250.923773303</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>3297.03</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1657673.310373197</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Pipeline volume [m³] by diameter x scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>bm_dense_2</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>bm_sco2</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>ins100</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>ins20</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>ins40</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>ins60</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>ins80</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins20</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins40</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins60</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="inlineStr">
+        <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>6"</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>3459.677057482731</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>14450.5271084924</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>9271.409159739389</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>3032.279433013573</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>1835.091806299497</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>8273.783206593072</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>10"</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>6440.252059329197</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>14"</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>23191.96078169414</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>18"</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>111810.1736791497</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>23268.27092804623</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>23268.27092804623</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>12825.21219853927</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>12825.21219853927</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>59204.14776033324</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>36093.4831265855</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>12825.21219853927</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>20258.97574628452</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>16515.82625669548</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>23268.27092804623</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>22"</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>34758.77509004436</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>144832.725726216</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>19158.65032127471</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>34758.77509004436</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>34758.77509004436</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>53917.42541131907</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>34758.77509004436</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>34758.77509004436</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>34758.77509004436</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>26"</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>229799.3815780042</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>127902.2911418238</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>34458.94614051279</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>273335.4854990696</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>334810.108400042</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>188198.5962026038</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>153739.650062091</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>306783.9555847661</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>245309.3326837936</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>245309.3326837936</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>229799.3815780042</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>158415.2426547153</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>30"</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>326467.5751226851</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>140783.0992849697</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>342465.3436527512</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>326526.8598977395</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>230453.6017384166</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>230453.6017384166</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>295128.730955463</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>311067.2147104748</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>198745.3678189325</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>198745.3678189325</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>198745.3678189325</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>198745.3678189325</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>342465.3436527512</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>34"</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>268333.8367777956</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>268333.8367777956</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>201481.7503524522</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>211972.6017313876</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>241810.9026383095</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>241810.9026383095</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>252301.7540172449</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>342783.1505836411</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>241810.9026383095</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>241810.9026383095</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>241810.9026383095</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>268333.8367777956</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>235074.7334111874</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>38"</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>367284.2205400324</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>346709.2214731844</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>346709.2214731844</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>367284.2205400324</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>42"</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>121713.1025042379</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>121713.1025042379</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>563364.4286287071</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>594603.8567885301</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>121713.1025042379</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>121713.1025042379</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>193425.2433128962</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>121713.1025042379</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>121713.1025042379</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>121713.1025042379</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>121713.1025042379</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>282129.1303109175</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>522891.7159798718</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="11" t="n"/>
+      <c r="K31" s="11" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="11" t="n"/>
+      <c r="N31" s="11" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline volume = pi * r^2 * length, r = nominal pipe diameter / 2 (no pipe-wall-thickness data is modeled, so the nominal diameter is used as the pipe's inner diameter). This is the pipe's own enclosed volume only -- it excludes the insulation shell (see the 'Insulation volume' tab) and is reported for every installed pipe in every scenario.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3570,7 +4492,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/analysis/EUS_full_analysis.xlsx
+++ b/analysis/EUS_full_analysis.xlsx
@@ -15,10 +15,12 @@
     <sheet name="Cost efficiency" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Cost category - supercritical" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Cost category - liquid" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Booster reason" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Pipe volume" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Insulation volume" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Booster vs insulation" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="CAPEX detail - supercritical" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="CAPEX detail - liquid" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Booster reason" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Pipe volume" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Insulation volume" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Booster vs insulation" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2889,6 +2891,4008 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX detail [M€] -- liquid scenarios, benchmark = bm_dense_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>CAPEX detail [M€]</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>bm_dense_2 (benchmark)</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins20</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins40</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins60</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CAPEX onshore pipeline (total, incl. insulation)</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>2488.57474523796</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>2542.379478390276</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>2494.415789195258</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>2513.738966388013</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>2435.149210437197</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX onshore insulation</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>96.84114258202197</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>30.55414562304001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX onshore pipeline without insulation</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2488.57474523796</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2542.379478390276</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2397.574646613236</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2513.738966388013</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>2404.595064814157</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX booster initial</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>23774.42934</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>23774.42934</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>23723.67947</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>23586.9629</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>23826.56291</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX booster additional</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>640.8729233911317</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>672.7545964307138</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>658.8419295946561</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>737.7173328301084</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>725.2013459129305</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>% deviation vs. dense-phase benchmark (bm_dense_2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CAPEX detail [M€]</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>bm_dense_2 (benchmark)</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins20</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins40</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins60</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>CAPEX onshore pipeline (total, incl. insulation)</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>2.162070207265198</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>0.2347144271424956</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>1.011190087748268</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>-2.146832635949402</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX onshore insulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX onshore pipeline without insulation</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>2.162070207265198</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>-3.656715507495122</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>1.011190087748268</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>-3.374609526376627</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX booster initial</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>-0.213464093182729</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>-0.788521302947077</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>0.2192842118497797</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX booster additional</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>4.974726170499228</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>2.803832951537835</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>15.11132798785313</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>13.15836875672343</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L94"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Per-pipe booster reason detail (EUS, boosted pipes only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Pipe ID</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Number of boosters</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Pressure at highest point [bar]</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Lowest pressure [bar]</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>p_min [bar]</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Temperature at critical pressure point [°C]</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>Lowest temperature [°C]</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>theta_min [°C]</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="L2" s="11" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ins100</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>25_a</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>27.09593705181401</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>27.12370763736967</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ins100</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>14_a</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>76.97104401094329</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>76.97104401094329</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>25.4791129998713</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>23.53838500964068</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ins100</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2_b</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>87.93509768253111</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>87.93509768253111</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>23.19354690367037</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>22.45514163646351</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ins100</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>10_a</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>123.5077344989185</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>123.2570465800274</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>37.26311717954779</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>37.53266853464079</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Inconclusive (installation-year snapshot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ins100</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>13_b</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>65.09457797059355</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>65.09457797059355</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>24.63421202281581</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>24.48554738510013</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ins100</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>31_a</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>96.01490431867812</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>96.01490431867812</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>36.28255339045213</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>36.6839072972405</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Pressure only</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>54_a</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>144.3664028948996</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>143.6069409160063</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>26.71025928518643</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>26.80997492935868</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Temperature only</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>60_b</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>90.69294174229272</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>90.69294174229272</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>24.46339143641816</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>22.22858476072506</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2_b</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>87.93509768253111</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>87.93509768253111</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>23.19354690367037</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>22.45514163646351</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>65_b</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>62.29813296627455</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>62.29813296627455</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>26.76040136691488</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>22.34896224971083</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>61_a</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>73.27503741519905</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>73.27503741519905</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>26.80692855889654</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>27.5098033169456</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>10_a</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>123.1245526439649</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>122.869494826188</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>23.21269847782931</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>23.46148378669019</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Temperature only</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>31_a</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>94.08777135878756</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>94.08777135878756</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>32.08262364503698</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>26.10570821868824</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>14_a</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>76.97104401094329</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>76.97104401094329</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>25.4791129998713</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>23.53838500964068</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>25_a</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>27.09593705181401</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>27.12370763736967</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ins20</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>10_a</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>127.6595181125517</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>127.4287791661388</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>38.5485018242337</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>38.81205954605867</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Inconclusive (installation-year snapshot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ins20</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>25_a</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>27.09593705181401</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>27.12370763736967</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ins20</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2_b</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>76.39458196087037</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>76.39458196087037</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>29.55171992167623</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>28.95222400973573</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ins20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>14_a</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>78.24018961694998</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>78.24018961694998</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>32.33945620699593</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>31.64011030605105</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ins20</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>31_a</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>96.01490431867812</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>96.01490431867812</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>36.28255339045213</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>36.6839072972405</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Pressure only</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ins20</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>13_b</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>84.59563676007875</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>84.59563676007875</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>25.44242266257267</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>25.29375802485699</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ins40</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>25_a</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>27.09593705181401</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>27.12370763736967</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ins40</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>14_a</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>78.24018961694998</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>78.24018961694998</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>32.33945620699593</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>31.64011030605105</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ins40</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2_b</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>76.39458196087037</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>76.39458196087037</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>29.55171992167623</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>28.95222400973573</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>ins40</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>31_a</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>96.01490431867812</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>96.01490431867812</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>36.28255339045213</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>36.6839072972405</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Pressure only</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ins40</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>13_b</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>84.59563676007966</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>84.59563676007966</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>25.44242266257289</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>25.29375802485721</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ins40</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>10_a</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>127.6595181125517</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>127.4287791661388</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>38.5485018242337</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>38.81205954605867</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Inconclusive (installation-year snapshot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ins60</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>14_a</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>76.97104401094329</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>76.97104401094329</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>25.4791129998713</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>23.53838500964068</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ins60</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>65_b</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>50.00000000000003</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>50.00000000000003</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>26.76040136691488</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>22.34896224971083</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ins60</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>25_a</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>27.09593705181401</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>27.12370763736967</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ins60</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>31_a</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>94.08777135878756</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>94.08777135878756</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>32.08262364503698</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>26.10570821868824</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ins60</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>61_a</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>83.98800344108297</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>83.98800344108297</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>29.81684785510058</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>30.51343096223421</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ins60</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>2_b</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>76.39458196087037</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>76.39458196087037</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>29.55171992167623</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>28.95222400973573</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ins80</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>31_a</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>96.01490431867812</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>96.01490431867812</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>36.28255339045213</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>36.6839072972405</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Pressure only</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ins80</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>14_a</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>76.97104401094329</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>76.97104401094329</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>25.4791129998713</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>23.53838500964068</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ins80</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>25_a</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>27.09593705181401</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>27.12370763736967</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ins80</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>2_b</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>76.39458196087037</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>76.39458196087037</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>29.55171992167623</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>28.95222400973573</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ins80</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>10_a</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>123.5077344989185</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>123.2570465800274</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>37.26311717954779</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>37.53266853464079</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Inconclusive (installation-year snapshot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ins80</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>13_b</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>65.09457797059358</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>65.09457797059358</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>24.63421202281575</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>24.48554738510007</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins20</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>2_b</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>72.70748558974221</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>72.70748558974221</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>11.52058370585532</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>11.01168039290185</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins20</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>31_a</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>87.35103979118902</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>87.35103979118902</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>18.3022023902338</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>15.34152481551364</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Pressure only</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins20</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>14_a</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>68.23071827897361</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>68.23071827897361</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>14.39816335964983</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>13.25316015337214</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins20</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>25_a</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>83.17668254091814</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>83.17668254091814</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>15.52172525613159</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>15.49390042686974</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Pressure only</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins20</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>13_b</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>52.60826380850764</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>52.60826380850764</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>12.93869871806898</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>12.44222419663431</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins40</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>2_b</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>72.70748558974221</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>72.70748558974221</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>11.52058370585532</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>11.01168039290185</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins40</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>14_a</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>68.23071827897361</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>68.23071827897361</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>14.39816335964983</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>13.25316015337214</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins40</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>31_a</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>87.35103979118902</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>87.35103979118902</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>18.3022023902338</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>15.34152481551364</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Pressure only</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins40</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>25_a</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>83.17668254091814</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>83.17668254091814</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>15.52172525613159</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>15.49390042686974</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Pressure only</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins40</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>13_b</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>52.60826380850764</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>52.60826380850764</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>12.93869871806898</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>12.44222419663431</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins40</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>10_a</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>127.5971856482135</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>127.5971856482135</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>23.13581066819184</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>15.11939448440599</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Inconclusive (installation-year snapshot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins60</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>25_a</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>83.17668254091814</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>83.17668254091814</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>15.52172525613159</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>15.49390042686974</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Pressure only</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins60</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>31_a</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>87.35103979118902</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>87.35103979118902</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>18.3022023902338</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>15.34152481551364</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Pressure only</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins60</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>13_b</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>72.94993796812295</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>72.94993796812295</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>12.70264080635081</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>12.20616628491614</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins60</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>14_a</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>68.23071827897361</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>68.23071827897361</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>14.39816335964983</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>13.25316015337214</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins60</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>2_b</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>72.70748558974221</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>72.70748558974221</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>11.52058370585532</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>11.01168039290185</v>
+      </c>
+      <c r="J57" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins60</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>41_a</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>135.087492546563</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>135.087492546563</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>7.685382375769827</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>7.488092528933219</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Temperature only</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>liq_ins60</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>10_a</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>127.5971856482135</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>127.5971856482135</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>23.13581066819184</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>15.11939448440599</v>
+      </c>
+      <c r="J59" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Inconclusive (installation-year snapshot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>25_a</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>83.17668254091814</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>83.17668254091814</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>15.52172525613159</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>15.49390042686974</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Pressure only</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>2_b</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>72.70748558974221</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>72.70748558974221</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>11.52058370585532</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>11.01168039290185</v>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>41_a</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>16.07897294360959</v>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Inconclusive (installation-year snapshot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>14_a</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>68.23071827897361</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>68.23071827897361</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>14.39816335964983</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>13.25316015337214</v>
+      </c>
+      <c r="J63" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>31_a</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>87.35103979118902</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>87.35103979118902</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>18.3022023902338</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>15.34152481551364</v>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Pressure only</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>10_a</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>127.5971856482135</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>127.5971856482135</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>23.13581066819184</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>15.11939448440599</v>
+      </c>
+      <c r="J65" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Inconclusive (installation-year snapshot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>13_b</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>72.94993796812173</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>72.94993796812173</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>12.70264080635134</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>12.20616628491667</v>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>10_a</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>123.1245526439649</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>122.869494826188</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>23.21269847782931</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>23.46148378669019</v>
+      </c>
+      <c r="J67" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Temperature only</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>59_a</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>66.22090372966993</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>66.22090372966993</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>22.24172757881252</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>22.23426138103358</v>
+      </c>
+      <c r="J68" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>14_a</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>76.97104401094329</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>76.97104401094329</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>25.4791129998713</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>23.53838500964068</v>
+      </c>
+      <c r="J69" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>2_b</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>87.93509768253111</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>87.93509768253111</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>23.19354690367037</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>22.45514163646351</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>31_a</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>94.08777135878756</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>94.08777135878756</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>32.08262364503698</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>26.10570821868824</v>
+      </c>
+      <c r="J71" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>65_b</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>86.95400932730499</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>86.95400932730499</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>32.62473401350245</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>25.56814634261212</v>
+      </c>
+      <c r="J72" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>25_a</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>27.09593705181401</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>27.12370763736967</v>
+      </c>
+      <c r="J73" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>5_a</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>113.3821431187982</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>113.3821431187982</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>35.77408120748448</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>35.14591303475528</v>
+      </c>
+      <c r="J74" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Inconclusive (installation-year snapshot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>Number of boosted pipes by reason x scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Reason for booster</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>ins100</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="inlineStr">
+        <is>
+          <t>ins20</t>
+        </is>
+      </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>ins40</t>
+        </is>
+      </c>
+      <c r="F77" s="1" t="inlineStr">
+        <is>
+          <t>ins60</t>
+        </is>
+      </c>
+      <c r="G77" s="1" t="inlineStr">
+        <is>
+          <t>ins80</t>
+        </is>
+      </c>
+      <c r="H77" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins20</t>
+        </is>
+      </c>
+      <c r="I77" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins40</t>
+        </is>
+      </c>
+      <c r="J77" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins60</t>
+        </is>
+      </c>
+      <c r="K77" s="1" t="inlineStr">
+        <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="L77" s="1" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Pressure only</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Temperature only</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J80" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K80" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L80" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Inconclusive (installation-year snapshot)</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L81" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>Total booster count by reason x scenario (sum of 'Number of boosters')</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>Reason for booster</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>ins100</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="inlineStr">
+        <is>
+          <t>ins20</t>
+        </is>
+      </c>
+      <c r="E84" s="1" t="inlineStr">
+        <is>
+          <t>ins40</t>
+        </is>
+      </c>
+      <c r="F84" s="1" t="inlineStr">
+        <is>
+          <t>ins60</t>
+        </is>
+      </c>
+      <c r="G84" s="1" t="inlineStr">
+        <is>
+          <t>ins80</t>
+        </is>
+      </c>
+      <c r="H84" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins20</t>
+        </is>
+      </c>
+      <c r="I84" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins40</t>
+        </is>
+      </c>
+      <c r="J84" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins60</t>
+        </is>
+      </c>
+      <c r="K84" s="1" t="inlineStr">
+        <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="L84" s="1" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Pressure only</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J85" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K85" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L85" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Temperature only</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J87" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K87" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L87" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Inconclusive (installation-year snapshot)</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L88" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89"/>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="n"/>
+      <c r="C91" s="11" t="n"/>
+      <c r="D91" s="11" t="n"/>
+      <c r="E91" s="11" t="n"/>
+      <c r="F91" s="11" t="n"/>
+      <c r="G91" s="11" t="n"/>
+      <c r="H91" s="11" t="n"/>
+      <c r="I91" s="11" t="n"/>
+      <c r="J91" s="11" t="n"/>
+      <c r="K91" s="11" t="n"/>
+      <c r="L91" s="11" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Reason is derived from the pipe's own Pressure/Temperature at critical point and Lowest pressure/temperature columns, which developed_solution.py computes from the raw simulated drop at the pipe's installation year -- i.e. the value WITHOUT the booster's compensation. A value already below p_min/theta_min there means that dimension needed the booster. p_min = 100 bar for every run; theta_min = 32°C (supercritical) / 15°C (liquid).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>'Inconclusive': neither value is below threshold at the pipe's installation-year snapshot -- can happen when the booster's own build year is later than the pipe's installation year (flows, and so the required pressure/temperature, change over time).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Excluded (older schema, no pressure/temperature columns exported): bm_dense_2, bm_sco2.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3804,7 +7808,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4492,7 +8496,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10177,3689 +14181,413 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="42" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Per-pipe booster reason detail (EUS, boosted pipes only)</t>
+          <t>CAPEX detail [M€] -- supercritical scenarios, benchmark = bm_sco2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Scenario</t>
+          <t>CAPEX detail [M€]</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Phase</t>
+          <t>bm_sco2 (benchmark)</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Pipe ID</t>
+          <t>noins</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Number of boosters</t>
+          <t>ins20</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Pressure at highest point [bar]</t>
+          <t>ins40</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>Lowest pressure [bar]</t>
+          <t>ins60</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>p_min [bar]</t>
+          <t>ins80</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>Temperature at critical pressure point [°C]</t>
+          <t>ins100</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>Lowest temperature [°C]</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>theta_min [°C]</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-      <c r="L2" s="11" t="n"/>
+          <t>ins150</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>ins100</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>25_a</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>87.38150101973842</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>87.38150101973842</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>27.09593705181401</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>27.12370763736967</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CAPEX onshore pipeline (total, incl. insulation)</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>2571.167083366353</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>3011.776373761153</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>2491.357005878346</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>2940.315261938953</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>2699.189907852268</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>3004.409742667825</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>3033.681652187734</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>2958.475102984037</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ins100</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>14_a</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>1</v>
+          <t>CAPEX onshore insulation</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>203.4100442235979</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>76.97104401094329</v>
+        <v>440.6946163934838</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>76.97104401094329</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>100</v>
+        <v>261.3010150016605</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>492.091138178896</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>25.4791129998713</v>
+        <v>234.26697045616</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>23.53838500964068</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
+        <v>165.67485359931</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ins100</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2_b</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>1</v>
+          <t>CAPEX onshore pipeline without insulation</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2571.167083366353</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>3011.776373761153</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2287.946961654748</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>87.93509768253111</v>
+        <v>2499.620645545469</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>87.93509768253111</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>100</v>
+        <v>2437.888892850608</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>2512.318604488929</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>23.19354690367037</v>
+        <v>2799.414681731574</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>22.45514163646351</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
+        <v>2792.800249384727</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ins100</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>10_a</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1</v>
+          <t>CAPEX booster initial</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>23586.9629</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>23819.94767</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>23926.32278</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>123.5077344989185</v>
+        <v>23679.19597</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>123.2570465800274</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>100</v>
+        <v>23826.56291</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>23631.47462</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>37.26311717954779</v>
+        <v>23774.42934</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>37.53266853464079</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Inconclusive (installation-year snapshot)</t>
-        </is>
+        <v>23606.99826</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>CAPEX booster additional</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>707.3223428982054</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1024.471405513181</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>726.569981355952</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>672.7418785888146</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>678.5620847975604</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>777.5900498603548</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>804.704814878888</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>1080.042504820924</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>% deviation vs. supercritical benchmark (bm_sco2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CAPEX detail [M€]</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>bm_sco2 (benchmark)</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>ins20</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>ins40</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>ins60</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>ins80</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
           <t>ins100</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>13_b</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>65.09457797059355</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>65.09457797059355</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>24.63421202281581</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>24.48554738510013</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>ins100</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>31_a</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>96.01490431867812</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>96.01490431867812</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>36.28255339045213</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>36.6839072972405</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Pressure only</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>ins150</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>54_a</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>144.3664028948996</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>143.6069409160063</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>26.71025928518643</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>26.80997492935868</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Temperature only</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>ins150</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>60_b</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>90.69294174229272</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>90.69294174229272</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>24.46339143641816</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>22.22858476072506</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>ins150</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2_b</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>87.93509768253111</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>87.93509768253111</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>23.19354690367037</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>22.45514163646351</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>CAPEX onshore pipeline (total, incl. insulation)</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>17.13654834978377</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>-3.104040884947616</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>14.35722248315676</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>4.97917172766145</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>16.85003911664271</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>17.98850692409396</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>15.06351034607185</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ins150</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>65_b</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>62.29813296627455</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>62.29813296627455</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>26.76040136691488</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>22.34896224971083</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
+          <t>CAPEX onshore insulation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ins150</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>61_a</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>73.27503741519905</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>73.27503741519905</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>26.80692855889654</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>27.5098033169456</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
+          <t>CAPEX onshore pipeline without insulation</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>17.13654834978377</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>-11.01523598150584</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>-2.782644437373937</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>-5.18356785826801</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>-2.288784702407415</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>8.877198212509136</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>8.619944127792598</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ins150</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>10_a</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>123.1245526439649</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>122.869494826188</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>23.21269847782931</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>23.46148378669019</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Temperature only</t>
-        </is>
+          <t>CAPEX booster initial</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>0.9877692646898714</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>1.438760392504793</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>0.3910341080835042</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>1.015815435907613</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>0.1887132319184775</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>0.7947883786258898</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>0.08494251712246377</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ins150</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>31_a</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>94.08777135878756</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>94.08777135878756</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>32.08262364503698</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>26.10570821868824</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>ins150</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>14_a</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>76.97104401094329</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>76.97104401094329</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>25.4791129998713</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>23.53838500964068</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>ins150</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>25_a</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>87.38150101973842</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>87.38150101973842</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>27.09593705181401</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>27.12370763736967</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>ins20</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>10_a</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>127.6595181125517</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>127.4287791661388</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>38.5485018242337</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>38.81205954605867</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Inconclusive (installation-year snapshot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>ins20</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>25_a</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>87.38150101973842</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>87.38150101973842</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>27.09593705181401</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>27.12370763736967</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>ins20</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>2_b</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>76.39458196087037</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>76.39458196087037</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>29.55171992167623</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>28.95222400973573</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>ins20</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>14_a</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>78.24018961694998</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>78.24018961694998</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>32.33945620699593</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>31.64011030605105</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>ins20</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>31_a</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>96.01490431867812</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>96.01490431867812</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>36.28255339045213</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>36.6839072972405</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Pressure only</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>ins20</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>13_b</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>84.59563676007875</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>84.59563676007875</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>25.44242266257267</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>25.29375802485699</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>ins40</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>25_a</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>87.38150101973842</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>87.38150101973842</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>27.09593705181401</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>27.12370763736967</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>ins40</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>14_a</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>78.24018961694998</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>78.24018961694998</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>32.33945620699593</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>31.64011030605105</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>ins40</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>2_b</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>76.39458196087037</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>76.39458196087037</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>29.55171992167623</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>28.95222400973573</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>ins40</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>31_a</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>96.01490431867812</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>96.01490431867812</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>36.28255339045213</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>36.6839072972405</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Pressure only</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>ins40</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>13_b</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>84.59563676007966</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>84.59563676007966</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>25.44242266257289</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>25.29375802485721</v>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>ins40</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>10_a</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>127.6595181125517</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>127.4287791661388</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>38.5485018242337</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>38.81205954605867</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Inconclusive (installation-year snapshot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>ins60</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>14_a</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>76.97104401094329</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>76.97104401094329</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>25.4791129998713</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>23.53838500964068</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>ins60</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>65_b</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>50.00000000000003</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>50.00000000000003</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>26.76040136691488</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>22.34896224971083</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>ins60</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>25_a</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>87.38150101973842</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>87.38150101973842</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>27.09593705181401</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>27.12370763736967</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>ins60</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>31_a</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>94.08777135878756</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>94.08777135878756</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>32.08262364503698</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>26.10570821868824</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>ins60</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>61_a</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>83.98800344108297</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>83.98800344108297</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>29.81684785510058</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>30.51343096223421</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>ins60</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>2_b</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>76.39458196087037</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>76.39458196087037</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>29.55171992167623</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>28.95222400973573</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>ins80</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>31_a</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>96.01490431867812</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>96.01490431867812</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>36.28255339045213</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>36.6839072972405</v>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Pressure only</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>ins80</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>14_a</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>76.97104401094329</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>76.97104401094329</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>25.4791129998713</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>23.53838500964068</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>ins80</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>25_a</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>87.38150101973842</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>87.38150101973842</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>27.09593705181401</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>27.12370763736967</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>ins80</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>2_b</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>76.39458196087037</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>76.39458196087037</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>29.55171992167623</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>28.95222400973573</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>ins80</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>10_a</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>123.5077344989185</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>123.2570465800274</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>37.26311717954779</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>37.53266853464079</v>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Inconclusive (installation-year snapshot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>ins80</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>13_b</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>65.09457797059358</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>65.09457797059358</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>24.63421202281575</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>24.48554738510007</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins20</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>2_b</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>72.70748558974221</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>72.70748558974221</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>11.52058370585532</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>11.01168039290185</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins20</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>31_a</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>87.35103979118902</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>87.35103979118902</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>18.3022023902338</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>15.34152481551364</v>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>Pressure only</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins20</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>14_a</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>68.23071827897361</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>68.23071827897361</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>14.39816335964983</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>13.25316015337214</v>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins20</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>25_a</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>83.17668254091814</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>83.17668254091814</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>15.52172525613159</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>15.49390042686974</v>
-      </c>
-      <c r="J45" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Pressure only</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins20</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>13_b</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>52.60826380850764</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>52.60826380850764</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>12.93869871806898</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>12.44222419663431</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins40</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>2_b</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>72.70748558974221</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>72.70748558974221</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H47" s="3" t="n">
-        <v>11.52058370585532</v>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>11.01168039290185</v>
-      </c>
-      <c r="J47" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins40</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>14_a</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>68.23071827897361</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>68.23071827897361</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H48" s="3" t="n">
-        <v>14.39816335964983</v>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>13.25316015337214</v>
-      </c>
-      <c r="J48" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins40</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>31_a</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>87.35103979118902</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>87.35103979118902</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>18.3022023902338</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>15.34152481551364</v>
-      </c>
-      <c r="J49" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Pressure only</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins40</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>25_a</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>83.17668254091814</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>83.17668254091814</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H50" s="3" t="n">
-        <v>15.52172525613159</v>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>15.49390042686974</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Pressure only</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins40</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>13_b</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>52.60826380850764</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>52.60826380850764</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H51" s="3" t="n">
-        <v>12.93869871806898</v>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>12.44222419663431</v>
-      </c>
-      <c r="J51" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins40</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>10_a</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>127.5971856482135</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>127.5971856482135</v>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H52" s="3" t="n">
-        <v>23.13581066819184</v>
-      </c>
-      <c r="I52" s="3" t="n">
-        <v>15.11939448440599</v>
-      </c>
-      <c r="J52" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>Inconclusive (installation-year snapshot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins60</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>25_a</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>83.17668254091814</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>83.17668254091814</v>
-      </c>
-      <c r="G53" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H53" s="3" t="n">
-        <v>15.52172525613159</v>
-      </c>
-      <c r="I53" s="3" t="n">
-        <v>15.49390042686974</v>
-      </c>
-      <c r="J53" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>Pressure only</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins60</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>31_a</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>87.35103979118902</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>87.35103979118902</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H54" s="3" t="n">
-        <v>18.3022023902338</v>
-      </c>
-      <c r="I54" s="3" t="n">
-        <v>15.34152481551364</v>
-      </c>
-      <c r="J54" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>Pressure only</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins60</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>13_b</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>72.94993796812295</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>72.94993796812295</v>
-      </c>
-      <c r="G55" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H55" s="3" t="n">
-        <v>12.70264080635081</v>
-      </c>
-      <c r="I55" s="3" t="n">
-        <v>12.20616628491614</v>
-      </c>
-      <c r="J55" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins60</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>14_a</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>68.23071827897361</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>68.23071827897361</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H56" s="3" t="n">
-        <v>14.39816335964983</v>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>13.25316015337214</v>
-      </c>
-      <c r="J56" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins60</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>2_b</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>72.70748558974221</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>72.70748558974221</v>
-      </c>
-      <c r="G57" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H57" s="3" t="n">
-        <v>11.52058370585532</v>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>11.01168039290185</v>
-      </c>
-      <c r="J57" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins60</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>41_a</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>135.087492546563</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>135.087492546563</v>
-      </c>
-      <c r="G58" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H58" s="3" t="n">
-        <v>7.685382375769827</v>
-      </c>
-      <c r="I58" s="3" t="n">
-        <v>7.488092528933219</v>
-      </c>
-      <c r="J58" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>Temperature only</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>liq_ins60</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>10_a</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>127.5971856482135</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>127.5971856482135</v>
-      </c>
-      <c r="G59" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H59" s="3" t="n">
-        <v>23.13581066819184</v>
-      </c>
-      <c r="I59" s="3" t="n">
-        <v>15.11939448440599</v>
-      </c>
-      <c r="J59" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>Inconclusive (installation-year snapshot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>liq_noins</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>25_a</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>83.17668254091814</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>83.17668254091814</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H60" s="3" t="n">
-        <v>15.52172525613159</v>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>15.49390042686974</v>
-      </c>
-      <c r="J60" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>Pressure only</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>liq_noins</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>2_b</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>72.70748558974221</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>72.70748558974221</v>
-      </c>
-      <c r="G61" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H61" s="3" t="n">
-        <v>11.52058370585532</v>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>11.01168039290185</v>
-      </c>
-      <c r="J61" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>liq_noins</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>41_a</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="F62" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="G62" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>16.07897294360959</v>
-      </c>
-      <c r="J62" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>Inconclusive (installation-year snapshot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>liq_noins</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>14_a</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>68.23071827897361</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>68.23071827897361</v>
-      </c>
-      <c r="G63" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>14.39816335964983</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>13.25316015337214</v>
-      </c>
-      <c r="J63" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>liq_noins</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>31_a</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>87.35103979118902</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>87.35103979118902</v>
-      </c>
-      <c r="G64" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>18.3022023902338</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>15.34152481551364</v>
-      </c>
-      <c r="J64" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>Pressure only</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>liq_noins</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>10_a</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>127.5971856482135</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>127.5971856482135</v>
-      </c>
-      <c r="G65" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>23.13581066819184</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>15.11939448440599</v>
-      </c>
-      <c r="J65" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>Inconclusive (installation-year snapshot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>liq_noins</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>liquid</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>13_b</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>72.94993796812173</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>72.94993796812173</v>
-      </c>
-      <c r="G66" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>12.70264080635134</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>12.20616628491667</v>
-      </c>
-      <c r="J66" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>noins</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>10_a</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>123.1245526439649</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>122.869494826188</v>
-      </c>
-      <c r="G67" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H67" s="3" t="n">
-        <v>23.21269847782931</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>23.46148378669019</v>
-      </c>
-      <c r="J67" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>Temperature only</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>noins</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>59_a</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>66.22090372966993</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>66.22090372966993</v>
-      </c>
-      <c r="G68" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>22.24172757881252</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>22.23426138103358</v>
-      </c>
-      <c r="J68" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>noins</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>14_a</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>76.97104401094329</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>76.97104401094329</v>
-      </c>
-      <c r="G69" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H69" s="3" t="n">
-        <v>25.4791129998713</v>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>23.53838500964068</v>
-      </c>
-      <c r="J69" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>noins</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>2_b</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>87.93509768253111</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>87.93509768253111</v>
-      </c>
-      <c r="G70" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H70" s="3" t="n">
-        <v>23.19354690367037</v>
-      </c>
-      <c r="I70" s="3" t="n">
-        <v>22.45514163646351</v>
-      </c>
-      <c r="J70" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>noins</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>31_a</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>94.08777135878756</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>94.08777135878756</v>
-      </c>
-      <c r="G71" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>32.08262364503698</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>26.10570821868824</v>
-      </c>
-      <c r="J71" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>noins</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>65_b</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>86.95400932730499</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>86.95400932730499</v>
-      </c>
-      <c r="G72" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H72" s="3" t="n">
-        <v>32.62473401350245</v>
-      </c>
-      <c r="I72" s="3" t="n">
-        <v>25.56814634261212</v>
-      </c>
-      <c r="J72" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>noins</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>25_a</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>87.38150101973842</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>87.38150101973842</v>
-      </c>
-      <c r="G73" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H73" s="3" t="n">
-        <v>27.09593705181401</v>
-      </c>
-      <c r="I73" s="3" t="n">
-        <v>27.12370763736967</v>
-      </c>
-      <c r="J73" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>noins</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>supercritical</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>5_a</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>113.3821431187982</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>113.3821431187982</v>
-      </c>
-      <c r="G74" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H74" s="3" t="n">
-        <v>35.77408120748448</v>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>35.14591303475528</v>
-      </c>
-      <c r="J74" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>Inconclusive (installation-year snapshot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>Number of boosted pipes by reason x scenario</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>Reason for booster</t>
-        </is>
-      </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>ins100</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>ins150</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>ins20</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>ins40</t>
-        </is>
-      </c>
-      <c r="F77" s="1" t="inlineStr">
-        <is>
-          <t>ins60</t>
-        </is>
-      </c>
-      <c r="G77" s="1" t="inlineStr">
-        <is>
-          <t>ins80</t>
-        </is>
-      </c>
-      <c r="H77" s="1" t="inlineStr">
-        <is>
-          <t>liq_ins20</t>
-        </is>
-      </c>
-      <c r="I77" s="1" t="inlineStr">
-        <is>
-          <t>liq_ins40</t>
-        </is>
-      </c>
-      <c r="J77" s="1" t="inlineStr">
-        <is>
-          <t>liq_ins60</t>
-        </is>
-      </c>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>liq_noins</t>
-        </is>
-      </c>
-      <c r="L77" s="1" t="inlineStr">
-        <is>
-          <t>noins</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Pressure only</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I78" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K78" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L78" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>Temperature only</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F80" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G80" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H80" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I80" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J80" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K80" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L80" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Inconclusive (installation-year snapshot)</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K81" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L81" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82"/>
-    <row r="83">
-      <c r="A83" s="8" t="inlineStr">
-        <is>
-          <t>Total booster count by reason x scenario (sum of 'Number of boosters')</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="inlineStr">
-        <is>
-          <t>Reason for booster</t>
-        </is>
-      </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>ins100</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>ins150</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>ins20</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>ins40</t>
-        </is>
-      </c>
-      <c r="F84" s="1" t="inlineStr">
-        <is>
-          <t>ins60</t>
-        </is>
-      </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>ins80</t>
-        </is>
-      </c>
-      <c r="H84" s="1" t="inlineStr">
-        <is>
-          <t>liq_ins20</t>
-        </is>
-      </c>
-      <c r="I84" s="1" t="inlineStr">
-        <is>
-          <t>liq_ins40</t>
-        </is>
-      </c>
-      <c r="J84" s="1" t="inlineStr">
-        <is>
-          <t>liq_ins60</t>
-        </is>
-      </c>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>liq_noins</t>
-        </is>
-      </c>
-      <c r="L84" s="1" t="inlineStr">
-        <is>
-          <t>noins</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Pressure only</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I85" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J85" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K85" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L85" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Temperature only</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C87" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D87" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E87" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F87" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G87" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H87" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I87" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J87" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K87" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L87" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Inconclusive (installation-year snapshot)</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K88" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L88" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89"/>
-    <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="B91" s="11" t="n"/>
-      <c r="C91" s="11" t="n"/>
-      <c r="D91" s="11" t="n"/>
-      <c r="E91" s="11" t="n"/>
-      <c r="F91" s="11" t="n"/>
-      <c r="G91" s="11" t="n"/>
-      <c r="H91" s="11" t="n"/>
-      <c r="I91" s="11" t="n"/>
-      <c r="J91" s="11" t="n"/>
-      <c r="K91" s="11" t="n"/>
-      <c r="L91" s="11" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Reason is derived from the pipe's own Pressure/Temperature at critical point and Lowest pressure/temperature columns, which developed_solution.py computes from the raw simulated drop at the pipe's installation year -- i.e. the value WITHOUT the booster's compensation. A value already below p_min/theta_min there means that dimension needed the booster. p_min = 100 bar for every run; theta_min = 32°C (supercritical) / 15°C (liquid).</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>'Inconclusive': neither value is below threshold at the pipe's installation-year snapshot -- can happen when the booster's own build year is later than the pipe's installation year (flows, and so the required pressure/temperature, change over time).</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Excluded (older schema, no pressure/temperature columns exported): bm_dense_2, bm_sco2.</t>
-        </is>
+          <t>CAPEX booster additional</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>44.83798169240332</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>2.72119757717262</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>-4.888925771480604</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>-4.066075162110931</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>9.934325936069294</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>13.7677641542701</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>52.69452685398329</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/EUS_full_analysis.xlsx
+++ b/analysis/EUS_full_analysis.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1758,37 +1758,40 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>bm_dense_2</t>
+          <t>liq_ins150</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>benchmark (dense-phase network)</t>
-        </is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>150</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>44.06431895022087</v>
+        <v>44.18099571654832</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>13.72668578832562</v>
+        <v>13.78723479621761</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2445.26</v>
+        <v>2495.26</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>32.4</v>
+        <v>30.75</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>2637.546190737959</v>
+        <v>2586.491901579054</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>0</v>
@@ -1830,10 +1833,10 @@
         <v>0</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" s="4" t="n">
         <v>0</v>
@@ -1854,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="AG8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH8" s="4" t="n">
         <v>2</v>
@@ -1866,7 +1869,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AL8" s="4" t="n">
         <v>1</v>
@@ -1878,19 +1881,19 @@
         <v>0</v>
       </c>
       <c r="AO8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="AP8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="AT8" s="4" t="n">
         <v>1</v>
@@ -1917,37 +1920,37 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>bm_sco2</t>
+          <t>bm_dense_2</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>benchmark (sCO2 network)</t>
+          <t>benchmark (dense-phase network)</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>44.09945815367178</v>
+        <v>44.06431895022087</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>13.96324914365908</v>
+        <v>13.72668578832562</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>2997.59</v>
+        <v>2445.26</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>28.35294117647059</v>
+        <v>32.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>2736.276466706352</v>
+        <v>2637.546190737959</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>0</v>
@@ -1965,10 +1968,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" s="4" t="n">
         <v>0</v>
@@ -1989,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="4" t="n">
         <v>0</v>
@@ -2001,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD9" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="4" t="n">
         <v>0</v>
@@ -2016,7 +2019,7 @@
         <v>2</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI9" s="4" t="n">
         <v>0</v>
@@ -2025,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL9" s="4" t="n">
         <v>1</v>
@@ -2076,94 +2079,94 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>noins</t>
+          <t>bm_sco2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>supercritical</t>
+          <t>benchmark (sCO2 network)</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>45.20868279931497</v>
+        <v>44.09945815367178</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14.85183782931498</v>
+        <v>13.96324914365908</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3297.03</v>
+        <v>2997.59</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>30</v>
+        <v>7</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>28.35294117647059</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>3160.747819261153</v>
+        <v>2736.276466706352</v>
       </c>
       <c r="L10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="N10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AD10" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE10" s="4" t="n">
         <v>0</v>
@@ -2184,32 +2187,32 @@
         <v>0</v>
       </c>
       <c r="AK10" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AL10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AM10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" s="4" t="n">
+      <c r="AP10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="AP10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="AT10" s="4" t="n">
         <v>1</v>
       </c>
@@ -2220,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="AW10" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX10" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY10" s="4" t="n">
         <v>0</v>
@@ -2235,7 +2238,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ins20</t>
+          <t>noins</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -2243,38 +2246,35 @@
           <t>supercritical</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>20</v>
-      </c>
       <c r="D11" s="3" t="n">
-        <v>44.36860295543205</v>
+        <v>45.20868279931497</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>14.02511458813818</v>
+        <v>14.85183782931498</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2394.66</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>43.47548294956277</v>
+        <v>3297.03</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>31.06666666666667</v>
+        <v>8</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>30</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>2640.328451378346</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>203.4100442235979</v>
+        <v>3160.747819261153</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -2313,7 +2313,7 @@
         <v>1</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11" s="4" t="n">
         <v>0</v>
@@ -2322,40 +2322,40 @@
         <v>0</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" s="3" t="n">
-        <v>141.73</v>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="AG11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AH11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ11" s="3" t="n">
-        <v>670.88</v>
-      </c>
-      <c r="AK11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL11" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AM11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN11" s="3" t="n">
-        <v>228.48</v>
+        <v>0</v>
+      </c>
+      <c r="AN11" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="AO11" s="4" t="n">
         <v>2</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="AS11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT11" s="4" t="n">
         <v>1</v>
@@ -2382,10 +2382,10 @@
         <v>0</v>
       </c>
       <c r="AW11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY11" s="4" t="n">
         <v>0</v>
@@ -2397,7 +2397,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ins40</t>
+          <t>ins20</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2406,34 +2406,34 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>44.5896792151083</v>
+        <v>44.36860295543205</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>14.52751772781437</v>
+        <v>14.02511458813818</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2574.13</v>
+        <v>2394.66</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>47.41640865068975</v>
+        <v>43.47548294956277</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>30.75</v>
+        <v>31.06666666666667</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>3105.424645278953</v>
+        <v>2640.328451378346</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>440.6946163934831</v>
+        <v>203.4100442235979</v>
       </c>
       <c r="M12" s="4" t="n">
         <v>0</v>
@@ -2496,16 +2496,16 @@
         <v>141.73</v>
       </c>
       <c r="AG12" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH12" s="4" t="n">
         <v>2</v>
       </c>
       <c r="AI12" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ12" s="3" t="n">
-        <v>850.35</v>
+        <v>670.88</v>
       </c>
       <c r="AK12" s="4" t="n">
         <v>4</v>
@@ -2559,7 +2559,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ins60</t>
+          <t>ins40</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2568,118 +2568,118 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>44.36774617393734</v>
+        <v>44.5896792151083</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>14.02141706218577</v>
+        <v>14.52751772781437</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>3035.1</v>
+        <v>2574.13</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>30.73539586834041</v>
+        <v>47.41640865068975</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>6</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>27.55555555555556</v>
+        <v>30.75</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>2848.161353352268</v>
+        <v>3105.424645278953</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>261.3010150016603</v>
+        <v>440.6946163934831</v>
       </c>
       <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="3" t="n">
+        <v>141.73</v>
+      </c>
+      <c r="AG13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="N13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>78.12</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB13" s="3" t="n">
-        <v>360.62</v>
-      </c>
-      <c r="AC13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI13" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AJ13" s="3" t="n">
-        <v>448.83</v>
+        <v>850.35</v>
       </c>
       <c r="AK13" s="4" t="n">
         <v>4</v>
       </c>
       <c r="AL13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>45.28</v>
+        <v>228.48</v>
       </c>
       <c r="AO13" s="4" t="n">
         <v>2</v>
@@ -2706,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="AW13" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX13" s="4" t="n">
         <v>0</v>
@@ -2721,7 +2721,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ins80</t>
+          <t>ins60</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2730,46 +2730,46 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>44.77214112019545</v>
+        <v>44.36774617393734</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>14.5180377170776</v>
+        <v>14.02141706218577</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>2560.89</v>
+        <v>3035.1</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>31.98263103842805</v>
+        <v>30.73539586834041</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>6</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>30.25</v>
+        <v>27.55555555555556</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>3153.381188167823</v>
+        <v>2848.161353352268</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>492.0911381788895</v>
+        <v>261.3010150016603</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>78.12</v>
       </c>
       <c r="Q14" s="4" t="n">
         <v>0</v>
@@ -2802,10 +2802,10 @@
         <v>1</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB14" s="3" t="n">
-        <v>141.73</v>
+        <v>360.62</v>
       </c>
       <c r="AC14" s="4" t="n">
         <v>0</v>
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="AG14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH14" s="4" t="n">
         <v>1</v>
@@ -2841,10 +2841,10 @@
         <v>1</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>228.48</v>
+        <v>45.28</v>
       </c>
       <c r="AO14" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP14" s="4" t="n">
         <v>1</v>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="AW14" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX14" s="4" t="n">
         <v>0</v>
@@ -2883,7 +2883,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ins100</t>
+          <t>ins80</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -2892,34 +2892,34 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>44.92783528551593</v>
+        <v>44.77214112019545</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>14.57670902698809</v>
+        <v>14.5180377170776</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>16</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2659.17</v>
+        <v>2560.89</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>13.92201325977655</v>
+        <v>31.98263103842805</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>6</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>32.25</v>
+        <v>30.25</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>3182.653097687734</v>
+        <v>3153.381188167823</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>234.26697045616</v>
+        <v>492.0911381788895</v>
       </c>
       <c r="M15" s="4" t="n">
         <v>1</v>
@@ -2958,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z15" s="4" t="n">
         <v>1</v>
@@ -2985,16 +2985,16 @@
         <v>1</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AJ15" s="3" t="n">
+        <v>448.83</v>
       </c>
       <c r="AK15" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL15" s="4" t="n">
         <v>2</v>
@@ -3006,7 +3006,7 @@
         <v>228.48</v>
       </c>
       <c r="AO15" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AP15" s="4" t="n">
         <v>1</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="AS15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT15" s="4" t="n">
         <v>1</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AW15" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY15" s="4" t="n">
         <v>0</v>
@@ -3045,7 +3045,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ins150</t>
+          <t>ins100</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -3054,46 +3054,46 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>45.12111740375148</v>
+        <v>44.92783528551593</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>14.99495176761194</v>
+        <v>14.57670902698809</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3311.17</v>
+        <v>2659.17</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>12.2585068117916</v>
+        <v>13.92201325977655</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>25.6</v>
+        <v>32.25</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>3107.446548484038</v>
+        <v>3182.653097687734</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>165.6748535993072</v>
+        <v>234.26697045616</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>172.38</v>
+        <v>0</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
@@ -3108,16 +3108,16 @@
         <v>0</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>233.52</v>
+        <v>0</v>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="Y16" s="4" t="n">
         <v>1</v>
@@ -3126,13 +3126,13 @@
         <v>1</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AB16" s="3" t="n">
+        <v>141.73</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16" s="4" t="n">
         <v>0</v>
@@ -3144,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="AG16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH16" s="4" t="n">
         <v>0</v>
@@ -3162,10 +3162,10 @@
         <v>2</v>
       </c>
       <c r="AM16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AN16" s="3" t="n">
+        <v>228.48</v>
       </c>
       <c r="AO16" s="4" t="n">
         <v>1</v>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="AS16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT16" s="4" t="n">
         <v>1</v>
@@ -3201,6 +3201,168 @@
         <v>0</v>
       </c>
       <c r="AZ16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>45.12111740375148</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>14.99495176761194</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>3311.17</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>12.2585068117916</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>3107.446548484038</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>165.6748535993072</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>172.38</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>233.52</v>
+      </c>
+      <c r="Y17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3215,7 +3377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3226,6 +3388,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3276,6 +3439,11 @@
           <t>liq_ins100</t>
         </is>
       </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins150</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -3304,6 +3472,9 @@
       <c r="H3" s="6" t="n">
         <v>2833.698782484014</v>
       </c>
+      <c r="I3" s="6" t="n">
+        <v>2437.520456079054</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3332,6 +3503,9 @@
       <c r="H4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="I4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3360,6 +3534,9 @@
       <c r="H5" s="3" t="n">
         <v>2833.698782484014</v>
       </c>
+      <c r="I5" s="3" t="n">
+        <v>2437.520456079054</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3388,6 +3565,9 @@
       <c r="H6" s="3" t="n">
         <v>24181.03304</v>
       </c>
+      <c r="I6" s="3" t="n">
+        <v>23826.56291</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3415,6 +3595,9 @@
       </c>
       <c r="H7" s="3" t="n">
         <v>700.6259099927481</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>753.540610836992</v>
       </c>
     </row>
     <row r="8"/>
@@ -3466,6 +3649,11 @@
           <t>liq_ins100</t>
         </is>
       </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins150</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -3494,6 +3682,9 @@
       <c r="H11" s="10" t="n">
         <v>13.86834122247965</v>
       </c>
+      <c r="I11" s="10" t="n">
+        <v>-2.051547346793648</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3529,6 +3720,9 @@
       <c r="H13" s="9" t="n">
         <v>13.86834122247965</v>
       </c>
+      <c r="I13" s="9" t="n">
+        <v>-2.051547346793648</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3557,6 +3751,9 @@
       <c r="H14" s="9" t="n">
         <v>1.710256402730547</v>
       </c>
+      <c r="I14" s="9" t="n">
+        <v>0.2192842118497797</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3584,6 +3781,9 @@
       </c>
       <c r="H15" s="9" t="n">
         <v>9.323687180515892</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>17.58034757494317</v>
       </c>
     </row>
   </sheetData>
@@ -3597,7 +3797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N108"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3613,7 +3813,8 @@
     <col width="42" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3682,6 +3883,7 @@
       <c r="L2" s="11" t="n"/>
       <c r="M2" s="11" t="n"/>
       <c r="N2" s="11" t="n"/>
+      <c r="O2" s="11" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -5707,7 +5909,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>liq_ins20</t>
+          <t>liq_ins150</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -5717,40 +5919,40 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>72.70748558974221</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>72.70748558974221</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="G50" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>11.52058370585532</v>
+        <v>18.3022023902338</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>11.01168039290185</v>
+        <v>15.34152481551364</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>liq_ins20</t>
+          <t>liq_ins150</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -5760,26 +5962,26 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>87.35103979118902</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>87.35103979118902</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="G51" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>18.3022023902338</v>
+        <v>15.52172525613159</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>15.34152481551364</v>
+        <v>15.49390042686974</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>15</v>
@@ -5793,7 +5995,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>liq_ins20</t>
+          <t>liq_ins150</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -5836,7 +6038,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>liq_ins20</t>
+          <t>liq_ins150</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -5846,40 +6048,40 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>10_a</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>83.17668254091814</v>
+        <v>127.5971856482135</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>83.17668254091814</v>
+        <v>127.5971856482135</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>15.52172525613159</v>
+        <v>23.13581066819184</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>15.49390042686974</v>
+        <v>15.11939448440599</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Inconclusive (installation-year snapshot)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>liq_ins20</t>
+          <t>liq_ins150</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -5896,19 +6098,19 @@
         <v>1</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>52.60826380850764</v>
+        <v>72.94993796812196</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>52.60826380850764</v>
+        <v>72.94993796812196</v>
       </c>
       <c r="G54" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>12.93869871806898</v>
+        <v>12.70264080635227</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>12.44222419663431</v>
+        <v>12.2061662849176</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>15</v>
@@ -5922,7 +6124,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>liq_ins40</t>
+          <t>liq_ins150</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -5965,7 +6167,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>liq_ins40</t>
+          <t>liq_ins150</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -5975,40 +6177,40 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>41_a</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E56" s="3" t="n">
-        <v>68.23071827897361</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>68.23071827897361</v>
+      <c r="E56" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>150</v>
       </c>
       <c r="G56" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="H56" s="3" t="n">
-        <v>14.39816335964983</v>
+      <c r="H56" s="4" t="n">
+        <v>25</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>13.25316015337214</v>
+        <v>16.07897294360959</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Inconclusive (installation-year snapshot)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>liq_ins40</t>
+          <t>liq_ins20</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -6018,40 +6220,40 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>87.35103979118902</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>87.35103979118902</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="G57" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>18.3022023902338</v>
+        <v>11.52058370585532</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>15.34152481551364</v>
+        <v>11.01168039290185</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>liq_ins40</t>
+          <t>liq_ins20</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -6061,26 +6263,26 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>83.17668254091814</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>83.17668254091814</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="G58" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>15.52172525613159</v>
+        <v>18.3022023902338</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>15.49390042686974</v>
+        <v>15.34152481551364</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>15</v>
@@ -6094,7 +6296,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>liq_ins40</t>
+          <t>liq_ins20</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -6104,26 +6306,26 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>13_b</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>52.60826380850764</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>52.60826380850764</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="G59" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>12.93869871806898</v>
+        <v>14.39816335964983</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>12.44222419663431</v>
+        <v>13.25316015337214</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>15</v>
@@ -6137,7 +6339,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>liq_ins40</t>
+          <t>liq_ins20</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -6147,40 +6349,40 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>10_a</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>127.5971856482135</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>127.5971856482135</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="G60" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>23.13581066819184</v>
+        <v>15.52172525613159</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>15.11939448440599</v>
+        <v>15.49390042686974</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Inconclusive (installation-year snapshot)</t>
+          <t>Pressure only</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>liq_ins60</t>
+          <t>liq_ins20</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -6190,40 +6392,40 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>83.17668254091814</v>
+        <v>52.60826380850764</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>83.17668254091814</v>
+        <v>52.60826380850764</v>
       </c>
       <c r="G61" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>15.52172525613159</v>
+        <v>12.93869871806898</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>15.49390042686974</v>
+        <v>12.44222419663431</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>liq_ins60</t>
+          <t>liq_ins40</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -6233,40 +6435,40 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>87.35103979118902</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>87.35103979118902</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="G62" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>18.3022023902338</v>
+        <v>11.52058370585532</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>15.34152481551364</v>
+        <v>11.01168039290185</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>liq_ins60</t>
+          <t>liq_ins40</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -6276,26 +6478,26 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>13_b</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>72.94993796812295</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>72.94993796812295</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="G63" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>12.70264080635081</v>
+        <v>14.39816335964983</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>12.20616628491614</v>
+        <v>13.25316015337214</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>15</v>
@@ -6309,7 +6511,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>liq_ins60</t>
+          <t>liq_ins40</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -6319,40 +6521,40 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>68.23071827897361</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>68.23071827897361</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="G64" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>14.39816335964983</v>
+        <v>18.3022023902338</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>13.25316015337214</v>
+        <v>15.34152481551364</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>liq_ins60</t>
+          <t>liq_ins40</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -6362,40 +6564,40 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D65" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>72.70748558974221</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>72.70748558974221</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="G65" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>11.52058370585532</v>
+        <v>15.52172525613159</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>11.01168039290185</v>
+        <v>15.49390042686974</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>liq_ins60</t>
+          <t>liq_ins40</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -6405,40 +6607,40 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>41_a</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>135.087492546563</v>
+        <v>52.60826380850764</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>135.087492546563</v>
+        <v>52.60826380850764</v>
       </c>
       <c r="G66" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>7.685382375769827</v>
+        <v>12.93869871806898</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>7.488092528933219</v>
+        <v>12.44222419663431</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Temperature only</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>liq_ins60</t>
+          <t>liq_ins40</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -6481,7 +6683,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>liq_ins80</t>
+          <t>liq_ins60</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -6491,40 +6693,40 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>10_a</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>127.5971856482135</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>127.5971856482135</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="G68" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>23.13581066819184</v>
+        <v>15.52172525613159</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>15.11939448440599</v>
+        <v>15.49390042686974</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Inconclusive (installation-year snapshot)</t>
+          <t>Pressure only</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>liq_ins80</t>
+          <t>liq_ins60</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -6534,40 +6736,40 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>13_b</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D69" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>72.9499379681217</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>72.9499379681217</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="G69" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>12.70264080635134</v>
+        <v>18.3022023902338</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>12.20616628491667</v>
+        <v>15.34152481551364</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>liq_ins80</t>
+          <t>liq_ins60</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -6577,40 +6779,40 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>87.35103979118902</v>
+        <v>72.94993796812295</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>87.35103979118902</v>
+        <v>72.94993796812295</v>
       </c>
       <c r="G70" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>18.3022023902338</v>
+        <v>12.70264080635081</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>15.34152481551364</v>
+        <v>12.20616628491614</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>liq_ins80</t>
+          <t>liq_ins60</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -6653,7 +6855,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>liq_ins80</t>
+          <t>liq_ins60</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -6663,40 +6865,40 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>83.17668254091814</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>83.17668254091814</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="G72" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>15.52172525613159</v>
+        <v>11.52058370585532</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>15.49390042686974</v>
+        <v>11.01168039290185</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>liq_ins80</t>
+          <t>liq_ins60</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -6706,40 +6908,40 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>41_a</t>
         </is>
       </c>
       <c r="D73" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>72.70748558974221</v>
+        <v>135.087492546563</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>72.70748558974221</v>
+        <v>135.087492546563</v>
       </c>
       <c r="G73" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>11.52058370585532</v>
+        <v>7.685382375769827</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>11.01168039290185</v>
+        <v>7.488092528933219</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Temperature only</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>liq_noins</t>
+          <t>liq_ins60</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -6749,40 +6951,40 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>10_a</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>83.17668254091814</v>
+        <v>127.5971856482135</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>83.17668254091814</v>
+        <v>127.5971856482135</v>
       </c>
       <c r="G74" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>15.52172525613159</v>
+        <v>23.13581066819184</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>15.49390042686974</v>
+        <v>15.11939448440599</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Inconclusive (installation-year snapshot)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>liq_noins</t>
+          <t>liq_ins80</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -6792,40 +6994,40 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>10_a</t>
         </is>
       </c>
       <c r="D75" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>72.70748558974221</v>
+        <v>127.5971856482135</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>72.70748558974221</v>
+        <v>127.5971856482135</v>
       </c>
       <c r="G75" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>11.52058370585532</v>
+        <v>23.13581066819184</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>11.01168039290185</v>
+        <v>15.11939448440599</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Inconclusive (installation-year snapshot)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>liq_noins</t>
+          <t>liq_ins80</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -6835,40 +7037,40 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>41_a</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E76" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="F76" s="4" t="n">
-        <v>150</v>
+      <c r="E76" s="3" t="n">
+        <v>72.9499379681217</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>72.9499379681217</v>
       </c>
       <c r="G76" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="H76" s="4" t="n">
-        <v>25</v>
+      <c r="H76" s="3" t="n">
+        <v>12.70264080635134</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>16.07897294360959</v>
+        <v>12.20616628491667</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Inconclusive (installation-year snapshot)</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>liq_noins</t>
+          <t>liq_ins80</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -6878,40 +7080,40 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>31_a</t>
         </is>
       </c>
       <c r="D77" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>68.23071827897361</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>68.23071827897361</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="G77" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>14.39816335964983</v>
+        <v>18.3022023902338</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>13.25316015337214</v>
+        <v>15.34152481551364</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>liq_noins</t>
+          <t>liq_ins80</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -6921,40 +7123,40 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>31_a</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>87.35103979118902</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>87.35103979118902</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="G78" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>18.3022023902338</v>
+        <v>14.39816335964983</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>15.34152481551364</v>
+        <v>13.25316015337214</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Pressure only</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>liq_noins</t>
+          <t>liq_ins80</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -6964,40 +7166,40 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>10_a</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D79" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>127.5971856482135</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>127.5971856482135</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="G79" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>23.13581066819184</v>
+        <v>15.52172525613159</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>15.11939448440599</v>
+        <v>15.49390042686974</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Inconclusive (installation-year snapshot)</t>
+          <t>Pressure only</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>liq_noins</t>
+          <t>liq_ins80</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -7007,26 +7209,26 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>13_b</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>72.94993796812173</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>72.94993796812173</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="G80" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>12.70264080635134</v>
+        <v>11.52058370585532</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>12.20616628491667</v>
+        <v>11.01168039290185</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>15</v>
@@ -7040,82 +7242,82 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>noins</t>
+          <t>liq_noins</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>supercritical</t>
+          <t>liquid</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>10_a</t>
+          <t>25_a</t>
         </is>
       </c>
       <c r="D81" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>123.1245526439649</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>122.869494826188</v>
+        <v>83.17668254091814</v>
       </c>
       <c r="G81" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>23.21269847782931</v>
+        <v>15.52172525613159</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>23.46148378669019</v>
+        <v>15.49390042686974</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Temperature only</t>
+          <t>Pressure only</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>noins</t>
+          <t>liq_noins</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>supercritical</t>
+          <t>liquid</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>59_a</t>
+          <t>2_b</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>66.22090372966993</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>66.22090372966993</v>
+        <v>72.70748558974221</v>
       </c>
       <c r="G82" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>22.24172757881252</v>
+        <v>11.52058370585532</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>22.23426138103358</v>
+        <v>11.01168039290185</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -7126,82 +7328,82 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>noins</t>
+          <t>liq_noins</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>supercritical</t>
+          <t>liquid</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>14_a</t>
+          <t>41_a</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E83" s="3" t="n">
-        <v>76.97104401094329</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>76.97104401094329</v>
+      <c r="E83" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>150</v>
       </c>
       <c r="G83" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="H83" s="3" t="n">
-        <v>25.4791129998713</v>
+      <c r="H83" s="4" t="n">
+        <v>25</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>23.53838500964068</v>
+        <v>16.07897294360959</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Inconclusive (installation-year snapshot)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>noins</t>
+          <t>liq_noins</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>supercritical</t>
+          <t>liquid</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>2_b</t>
+          <t>14_a</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>87.93509768253111</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>87.93509768253111</v>
+        <v>68.23071827897361</v>
       </c>
       <c r="G84" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>23.19354690367037</v>
+        <v>14.39816335964983</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>22.45514163646351</v>
+        <v>13.25316015337214</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -7212,12 +7414,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>noins</t>
+          <t>liq_noins</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>supercritical</t>
+          <t>liquid</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -7229,108 +7431,108 @@
         <v>1</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>94.08777135878756</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>94.08777135878756</v>
+        <v>87.35103979118902</v>
       </c>
       <c r="G85" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>32.08262364503698</v>
+        <v>18.3022023902338</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>26.10570821868824</v>
+        <v>15.34152481551364</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Pressure only</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>noins</t>
+          <t>liq_noins</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>supercritical</t>
+          <t>liquid</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>65_b</t>
+          <t>10_a</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>86.95400932730499</v>
+        <v>127.5971856482135</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>86.95400932730499</v>
+        <v>127.5971856482135</v>
       </c>
       <c r="G86" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>32.62473401350245</v>
+        <v>23.13581066819184</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>25.56814634261212</v>
+        <v>15.11939448440599</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Inconclusive (installation-year snapshot)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>noins</t>
+          <t>liq_noins</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>supercritical</t>
+          <t>liquid</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>25_a</t>
+          <t>13_b</t>
         </is>
       </c>
       <c r="D87" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>87.38150101973842</v>
+        <v>72.94993796812173</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>87.38150101973842</v>
+        <v>72.94993796812173</v>
       </c>
       <c r="G87" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>27.09593705181401</v>
+        <v>12.70264080635134</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>27.12370763736967</v>
+        <v>12.20616628491667</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -7351,305 +7553,342 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>5_a</t>
+          <t>10_a</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>113.3821431187982</v>
+        <v>123.1245526439649</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>113.3821431187982</v>
+        <v>122.869494826188</v>
       </c>
       <c r="G88" s="4" t="n">
         <v>100</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>35.77408120748448</v>
+        <v>23.21269847782931</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>35.14591303475528</v>
+        <v>23.46148378669019</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Inconclusive (installation-year snapshot)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89"/>
+          <t>Temperature only</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>59_a</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>66.22090372966993</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>66.22090372966993</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>22.24172757881252</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>22.23426138103358</v>
+      </c>
+      <c r="J89" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>Number of boosted pipes by reason x scenario</t>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>14_a</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>76.97104401094329</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>76.97104401094329</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>25.4791129998713</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>23.53838500964068</v>
+      </c>
+      <c r="J90" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="inlineStr">
-        <is>
-          <t>Reason for booster</t>
-        </is>
-      </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>ins100</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>ins150</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>ins20</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>ins40</t>
-        </is>
-      </c>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>ins60</t>
-        </is>
-      </c>
-      <c r="G91" s="1" t="inlineStr">
-        <is>
-          <t>ins80</t>
-        </is>
-      </c>
-      <c r="H91" s="1" t="inlineStr">
-        <is>
-          <t>liq_ins100</t>
-        </is>
-      </c>
-      <c r="I91" s="1" t="inlineStr">
-        <is>
-          <t>liq_ins20</t>
-        </is>
-      </c>
-      <c r="J91" s="1" t="inlineStr">
-        <is>
-          <t>liq_ins40</t>
-        </is>
-      </c>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>liq_ins60</t>
-        </is>
-      </c>
-      <c r="L91" s="1" t="inlineStr">
-        <is>
-          <t>liq_ins80</t>
-        </is>
-      </c>
-      <c r="M91" s="1" t="inlineStr">
-        <is>
-          <t>liq_noins</t>
-        </is>
-      </c>
-      <c r="N91" s="1" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>noins</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>2_b</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>87.93509768253111</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>87.93509768253111</v>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>23.19354690367037</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>22.45514163646351</v>
+      </c>
+      <c r="J91" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Pressure only</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C92" s="4" t="n">
-        <v>0</v>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>31_a</t>
+        </is>
       </c>
       <c r="D92" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E92" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="4" t="n">
-        <v>0</v>
+      <c r="E92" s="3" t="n">
+        <v>94.08777135878756</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>94.08777135878756</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I92" s="4" t="n">
-        <v>2</v>
+        <v>100</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>32.08262364503698</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>26.10570821868824</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K92" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L92" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M92" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N92" s="4" t="n">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Temperature only</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" s="4" t="n">
-        <v>2</v>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>65_b</t>
+        </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>86.95400932730499</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>86.95400932730499</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I93" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>32.62473401350245</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>25.56814634261212</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" s="4" t="n">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>25_a</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>87.38150101973842</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>27.09593705181401</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>27.12370763736967</v>
+      </c>
+      <c r="J94" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
           <t>Both</t>
         </is>
-      </c>
-      <c r="B94" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C94" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D94" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E94" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F94" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G94" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H94" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I94" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J94" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K94" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L94" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M94" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N94" s="4" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>noins</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>5_a</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>113.3821431187982</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>113.3821431187982</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>35.77408120748448</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>35.14591303475528</v>
+      </c>
+      <c r="J95" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
           <t>Inconclusive (installation-year snapshot)</t>
         </is>
-      </c>
-      <c r="B95" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M95" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N95" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="96"/>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>Total booster count by reason x scenario (sum of 'Number of boosters')</t>
+          <t>Number of boosted pipes by reason x scenario</t>
         </is>
       </c>
     </row>
@@ -7696,30 +7935,35 @@
       </c>
       <c r="I98" s="1" t="inlineStr">
         <is>
+          <t>liq_ins150</t>
+        </is>
+      </c>
+      <c r="J98" s="1" t="inlineStr">
+        <is>
           <t>liq_ins20</t>
         </is>
       </c>
-      <c r="J98" s="1" t="inlineStr">
+      <c r="K98" s="1" t="inlineStr">
         <is>
           <t>liq_ins40</t>
         </is>
       </c>
-      <c r="K98" s="1" t="inlineStr">
+      <c r="L98" s="1" t="inlineStr">
         <is>
           <t>liq_ins60</t>
         </is>
       </c>
-      <c r="L98" s="1" t="inlineStr">
+      <c r="M98" s="1" t="inlineStr">
         <is>
           <t>liq_ins80</t>
         </is>
       </c>
-      <c r="M98" s="1" t="inlineStr">
+      <c r="N98" s="1" t="inlineStr">
         <is>
           <t>liq_noins</t>
         </is>
       </c>
-      <c r="N98" s="1" t="inlineStr">
+      <c r="O98" s="1" t="inlineStr">
         <is>
           <t>noins</t>
         </is>
@@ -7768,6 +8012,9 @@
         <v>2</v>
       </c>
       <c r="N99" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O99" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7805,15 +8052,18 @@
         <v>0</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7860,6 +8110,9 @@
         <v>3</v>
       </c>
       <c r="N101" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O101" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7891,10 +8144,10 @@
         <v>1</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K102" s="4" t="n">
         <v>1</v>
@@ -7903,9 +8156,12 @@
         <v>1</v>
       </c>
       <c r="M102" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N102" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="N102" s="4" t="n">
+      <c r="O102" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7913,46 +8169,328 @@
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Total booster count by reason x scenario (sum of 'Number of boosters')</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="B105" s="11" t="n"/>
-      <c r="C105" s="11" t="n"/>
-      <c r="D105" s="11" t="n"/>
-      <c r="E105" s="11" t="n"/>
-      <c r="F105" s="11" t="n"/>
-      <c r="G105" s="11" t="n"/>
-      <c r="H105" s="11" t="n"/>
-      <c r="I105" s="11" t="n"/>
-      <c r="J105" s="11" t="n"/>
-      <c r="K105" s="11" t="n"/>
-      <c r="L105" s="11" t="n"/>
-      <c r="M105" s="11" t="n"/>
-      <c r="N105" s="11" t="n"/>
+          <t>Reason for booster</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>ins100</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t>ins20</t>
+        </is>
+      </c>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t>ins40</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="inlineStr">
+        <is>
+          <t>ins60</t>
+        </is>
+      </c>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>ins80</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins100</t>
+        </is>
+      </c>
+      <c r="I105" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins150</t>
+        </is>
+      </c>
+      <c r="J105" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins20</t>
+        </is>
+      </c>
+      <c r="K105" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins40</t>
+        </is>
+      </c>
+      <c r="L105" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins60</t>
+        </is>
+      </c>
+      <c r="M105" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins80</t>
+        </is>
+      </c>
+      <c r="N105" s="1" t="inlineStr">
+        <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="O105" s="1" t="inlineStr">
+        <is>
+          <t>noins</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Reason is derived from the pipe's own Pressure/Temperature at critical point and Lowest pressure/temperature columns, which developed_solution.py computes from the raw simulated drop at the pipe's installation year -- i.e. the value WITHOUT the booster's compensation. A value already below p_min/theta_min there means that dimension needed the booster. p_min = 100 bar for every run; theta_min = 32°C (supercritical) / 15°C (liquid).</t>
-        </is>
+          <t>Pressure only</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I106" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J106" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K106" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L106" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M106" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N106" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O106" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>'Inconclusive': neither value is below threshold at the pipe's installation-year snapshot -- can happen when the booster's own build year is later than the pipe's installation year (flows, and so the required pressure/temperature, change over time).</t>
-        </is>
+          <t>Temperature only</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D108" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H108" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I108" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J108" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K108" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L108" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M108" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N108" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O108" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Inconclusive (installation-year snapshot)</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M109" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N109" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O109" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110"/>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="n"/>
+      <c r="C112" s="11" t="n"/>
+      <c r="D112" s="11" t="n"/>
+      <c r="E112" s="11" t="n"/>
+      <c r="F112" s="11" t="n"/>
+      <c r="G112" s="11" t="n"/>
+      <c r="H112" s="11" t="n"/>
+      <c r="I112" s="11" t="n"/>
+      <c r="J112" s="11" t="n"/>
+      <c r="K112" s="11" t="n"/>
+      <c r="L112" s="11" t="n"/>
+      <c r="M112" s="11" t="n"/>
+      <c r="N112" s="11" t="n"/>
+      <c r="O112" s="11" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Reason is derived from the pipe's own Pressure/Temperature at critical point and Lowest pressure/temperature columns, which developed_solution.py computes from the raw simulated drop at the pipe's installation year -- i.e. the value WITHOUT the booster's compensation. A value already below p_min/theta_min there means that dimension needed the booster. p_min = 100 bar for every run; theta_min = 32°C (supercritical) / 15°C (liquid).</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>'Inconclusive': neither value is below threshold at the pipe's installation-year snapshot -- can happen when the booster's own build year is later than the pipe's installation year (flows, and so the required pressure/temperature, change over time).</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Excluded (older schema, no pressure/temperature columns exported): bm_dense_2, bm_sco2.</t>
         </is>
@@ -7969,7 +8507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7988,6 +8526,7 @@
     <col width="19" customWidth="1" min="14" max="14"/>
     <col width="19" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8034,6 +8573,7 @@
       <c r="N2" s="11" t="n"/>
       <c r="O2" s="11" t="n"/>
       <c r="P2" s="11" t="n"/>
+      <c r="Q2" s="11" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -8227,7 +8767,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>liq_ins20</t>
+          <t>liq_ins150</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -8236,19 +8776,19 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2422.78</v>
+        <v>2495.26</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1158939.359898479</v>
+        <v>1218387.740663737</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>liq_ins40</t>
+          <t>liq_ins20</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -8260,16 +8800,16 @@
         <v>15</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2394.66</v>
+        <v>2422.78</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1201871.914407041</v>
+        <v>1158939.359898479</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>liq_ins60</t>
+          <t>liq_ins40</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -8278,19 +8818,19 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2540.54</v>
+        <v>2394.66</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1211140.769761086</v>
+        <v>1201871.914407041</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>liq_ins80</t>
+          <t>liq_ins60</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -8299,19 +8839,19 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2445.26</v>
+        <v>2540.54</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1274406.887356857</v>
+        <v>1211140.769761086</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>liq_noins</t>
+          <t>liq_ins80</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -8326,189 +8866,163 @@
         <v>2445.26</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1266250.923773303</v>
+        <v>1274406.887356857</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>2445.26</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>1266250.923773303</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>noins</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>supercritical</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C18" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>3297.03</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>1657673.310373197</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Pipeline volume [m³] by diameter x scenario</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>Diameter</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>bm_dense_2</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>bm_sco2</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>ins100</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E21" s="1" t="inlineStr">
         <is>
           <t>ins150</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>ins20</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>ins40</t>
         </is>
       </c>
-      <c r="H20" s="1" t="inlineStr">
+      <c r="H21" s="1" t="inlineStr">
         <is>
           <t>ins60</t>
         </is>
       </c>
-      <c r="I20" s="1" t="inlineStr">
+      <c r="I21" s="1" t="inlineStr">
         <is>
           <t>ins80</t>
         </is>
       </c>
-      <c r="J20" s="1" t="inlineStr">
+      <c r="J21" s="1" t="inlineStr">
         <is>
           <t>liq_ins100</t>
         </is>
       </c>
-      <c r="K20" s="1" t="inlineStr">
+      <c r="K21" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins150</t>
+        </is>
+      </c>
+      <c r="L21" s="1" t="inlineStr">
         <is>
           <t>liq_ins20</t>
         </is>
       </c>
-      <c r="L20" s="1" t="inlineStr">
+      <c r="M21" s="1" t="inlineStr">
         <is>
           <t>liq_ins40</t>
         </is>
       </c>
-      <c r="M20" s="1" t="inlineStr">
+      <c r="N21" s="1" t="inlineStr">
         <is>
           <t>liq_ins60</t>
         </is>
       </c>
-      <c r="N20" s="1" t="inlineStr">
+      <c r="O21" s="1" t="inlineStr">
         <is>
           <t>liq_ins80</t>
         </is>
       </c>
-      <c r="O20" s="1" t="inlineStr">
+      <c r="P21" s="1" t="inlineStr">
         <is>
           <t>liq_noins</t>
         </is>
       </c>
-      <c r="P20" s="1" t="inlineStr">
+      <c r="Q21" s="1" t="inlineStr">
         <is>
           <t>noins</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>6"</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>3459.677057482731</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>14450.5271084924</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>9271.409159739389</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>3032.279433013573</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>4867.37123931307</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>1835.091806299497</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>8273.783206593072</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>10"</t>
+          <t>6"</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="3" t="n">
-        <v>6440.252059329197</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>0</v>
+      <c r="C22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>3459.677057482731</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>14450.5271084924</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>0</v>
@@ -8516,14 +9030,14 @@
       <c r="G22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>0</v>
+      <c r="H22" s="3" t="n">
+        <v>9271.409159739389</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>3032.279433013573</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>4867.37123931307</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>0</v>
@@ -8534,33 +9048,36 @@
       <c r="M22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="4" t="n">
-        <v>0</v>
+      <c r="N22" s="3" t="n">
+        <v>1835.091806299497</v>
       </c>
       <c r="O22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>8273.783206593072</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>14"</t>
+          <t>10"</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>0</v>
+      <c r="C23" s="3" t="n">
+        <v>6440.252059329197</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="3" t="n">
-        <v>23191.96078169414</v>
+      <c r="E23" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
@@ -8574,8 +9091,8 @@
       <c r="I23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="3" t="n">
-        <v>18836.01953518376</v>
+      <c r="J23" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>0</v>
@@ -8593,405 +9110,485 @@
         <v>0</v>
       </c>
       <c r="P23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>18"</t>
+          <t>14"</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="3" t="n">
-        <v>111810.1736791497</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>23268.27092804623</v>
+      <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>23268.27092804623</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>12825.21219853927</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>12825.21219853927</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>59204.14776033324</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>36093.4831265855</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>0</v>
+        <v>23191.96078169414</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>18836.01953518376</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="n">
-        <v>12825.21219853927</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>20258.97574628452</v>
+      <c r="L24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="n">
-        <v>16515.82625669548</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>23268.27092804623</v>
+      <c r="O24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22"</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>34758.77509004436</v>
+          <t>18"</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>144832.725726216</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>0</v>
+        <v>111810.1736791497</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>23268.27092804623</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>19158.65032127471</v>
+        <v>23268.27092804623</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>34758.77509004436</v>
+        <v>12825.21219853927</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>34758.77509004436</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>53917.42541131907</v>
+        <v>12825.21219853927</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>59204.14776033324</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>36093.4831265855</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>53917.42541131907</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>34758.77509004436</v>
+        <v>29341.03845523475</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>34758.77509004436</v>
+        <v>12825.21219853927</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>59430.56493029316</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>34758.77509004436</v>
-      </c>
-      <c r="P25" s="4" t="n">
-        <v>0</v>
+        <v>20258.97574628452</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>16515.82625669548</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>23268.27092804623</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26"</t>
+          <t>22"</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>229799.3815780042</v>
+        <v>34758.77509004436</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>127902.2911418238</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>34458.94614051279</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>0</v>
+        <v>144832.725726216</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>19158.65032127471</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>273335.4854990696</v>
+        <v>34758.77509004436</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>334810.108400042</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>188198.5962026038</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>153739.650062091</v>
+        <v>34758.77509004436</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>288845.436604859</v>
+        <v>53917.42541131907</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>306783.9555847661</v>
+        <v>34758.77509004436</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>245309.3326837936</v>
+        <v>53917.42541131907</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>245309.3326837936</v>
+        <v>34758.77509004436</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>229799.3815780042</v>
+        <v>34758.77509004436</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>229799.3815780042</v>
+        <v>59430.56493029316</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>158415.2426547153</v>
+        <v>34758.77509004436</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30"</t>
+          <t>26"</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>326467.5751226851</v>
+        <v>229799.3815780042</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>140783.0992849697</v>
+        <v>127902.2911418238</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>342465.3436527512</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>326526.8598977395</v>
+        <v>34458.94614051279</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>230453.6017384166</v>
+        <v>273335.4854990696</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>230453.6017384166</v>
+        <v>334810.108400042</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>295128.730955463</v>
+        <v>188198.5962026038</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>311067.2147104748</v>
+        <v>153739.650062091</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>140783.0992849697</v>
+        <v>288845.436604859</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>198745.3678189325</v>
+        <v>245309.3326837936</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>198745.3678189325</v>
+        <v>306783.9555847661</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>198745.3678189325</v>
+        <v>245309.3326837936</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>198745.3678189325</v>
+        <v>245309.3326837936</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>198745.3678189325</v>
+        <v>229799.3815780042</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>342465.3436527512</v>
+        <v>229799.3815780042</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>158415.2426547153</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>34"</t>
+          <t>30"</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>268333.8367777956</v>
+        <v>326467.5751226851</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>268333.8367777956</v>
+        <v>140783.0992849697</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>201481.7503524522</v>
+        <v>342465.3436527512</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>211972.6017313876</v>
+        <v>326526.8598977395</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>241810.9026383095</v>
+        <v>230453.6017384166</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>241810.9026383095</v>
+        <v>230453.6017384166</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>252301.7540172449</v>
+        <v>295128.730955463</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>342783.1505836411</v>
+        <v>311067.2147104748</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>346936.1453506234</v>
+        <v>140783.0992849697</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>241810.9026383095</v>
+        <v>198745.3678189325</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>241810.9026383095</v>
+        <v>198745.3678189325</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>241810.9026383095</v>
+        <v>198745.3678189325</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>268333.8367777956</v>
+        <v>198745.3678189325</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>268333.8367777956</v>
+        <v>198745.3678189325</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>235074.7334111874</v>
+        <v>198745.3678189325</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>342465.3436527512</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>38"</t>
+          <t>34"</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>235968.6059409137</v>
+        <v>268333.8367777956</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>235968.6059409137</v>
+        <v>268333.8367777956</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>367284.2205400324</v>
+        <v>201481.7503524522</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>235968.6059409137</v>
+        <v>211972.6017313876</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>235968.6059409137</v>
+        <v>241810.9026383095</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>235968.6059409137</v>
+        <v>241810.9026383095</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>235968.6059409137</v>
+        <v>252301.7540172449</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>235968.6059409137</v>
+        <v>342783.1505836411</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>346709.2214731844</v>
+        <v>346936.1453506234</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>235968.6059409137</v>
+        <v>241810.9026383095</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>346709.2214731844</v>
+        <v>241810.9026383095</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>346709.2214731844</v>
+        <v>241810.9026383095</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>235968.6059409137</v>
+        <v>241810.9026383095</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>235968.6059409137</v>
+        <v>268333.8367777956</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>367284.2205400324</v>
+        <v>268333.8367777956</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>235074.7334111874</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>38"</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>367284.2205400324</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>346709.2214731844</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>346709.2214731844</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>346709.2214731844</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>346709.2214731844</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>235968.6059409137</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>367284.2205400324</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>42"</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B31" s="3" t="n">
         <v>121713.1025042379</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C31" s="3" t="n">
         <v>121713.1025042379</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>563364.4286287071</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>594603.8567885301</v>
       </c>
-      <c r="F30" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>121713.1025042379</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G31" s="3" t="n">
         <v>121713.1025042379</v>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="H31" s="3" t="n">
         <v>193425.2433128962</v>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I31" s="3" t="n">
         <v>121713.1025042379</v>
       </c>
-      <c r="J30" s="3" t="n">
+      <c r="J31" s="3" t="n">
         <v>162185.8151530731</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K31" s="3" t="n">
         <v>121713.1025042379</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L31" s="3" t="n">
         <v>121713.1025042379</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M31" s="3" t="n">
         <v>121713.1025042379</v>
       </c>
-      <c r="N30" s="3" t="n">
+      <c r="N31" s="3" t="n">
+        <v>121713.1025042379</v>
+      </c>
+      <c r="O31" s="3" t="n">
         <v>282129.1303109175</v>
       </c>
-      <c r="O30" s="3" t="n">
+      <c r="P31" s="3" t="n">
         <v>282129.1303109175</v>
       </c>
-      <c r="P30" s="3" t="n">
+      <c r="Q31" s="3" t="n">
         <v>522891.7159798718</v>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="11" t="n"/>
-      <c r="J33" s="11" t="n"/>
-      <c r="K33" s="11" t="n"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="11" t="n"/>
-      <c r="N33" s="11" t="n"/>
-      <c r="O33" s="11" t="n"/>
-      <c r="P33" s="11" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="11" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="11" t="n"/>
+      <c r="I34" s="11" t="n"/>
+      <c r="J34" s="11" t="n"/>
+      <c r="K34" s="11" t="n"/>
+      <c r="L34" s="11" t="n"/>
+      <c r="M34" s="11" t="n"/>
+      <c r="N34" s="11" t="n"/>
+      <c r="O34" s="11" t="n"/>
+      <c r="P34" s="11" t="n"/>
+      <c r="Q34" s="11" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Pipeline volume = pi * r^2 * length, r = nominal pipe diameter / 2 (no pipe-wall-thickness data is modeled, so the nominal diameter is used as the pipe's inner diameter). This is the pipe's own enclosed volume only -- it excludes the insulation shell (see the 'Insulation volume' tab) and is reported for every installed pipe in every scenario.</t>
         </is>
@@ -9008,7 +9605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -9019,12 +9616,13 @@
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9073,6 +9671,7 @@
       <c r="L2" s="11" t="n"/>
       <c r="M2" s="11" t="n"/>
       <c r="N2" s="11" t="n"/>
+      <c r="O2" s="11" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -9258,7 +9857,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>liq_ins20</t>
+          <t>liq_ins150</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -9267,19 +9866,19 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>321.2</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>115877.9805497549</v>
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>liq_ins40</t>
+          <t>liq_ins20</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -9288,19 +9887,19 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>321.2</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>115877.9805497549</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>liq_ins60</t>
+          <t>liq_ins40</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -9309,19 +9908,19 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>45.28</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>12956.24980249203</v>
+        <v>0</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>liq_ins80</t>
+          <t>liq_ins60</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -9330,19 +9929,19 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>45.28</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>12956.24980249203</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>liq_noins</t>
+          <t>liq_ins80</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -9363,161 +9962,141 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>noins</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>supercritical</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="C18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Insulation shell volume [m³] by diameter x scenario</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>Diameter</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>ins100</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>ins150</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>ins20</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E21" s="1" t="inlineStr">
         <is>
           <t>ins40</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>ins60</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>ins80</t>
         </is>
       </c>
-      <c r="H20" s="1" t="inlineStr">
+      <c r="H21" s="1" t="inlineStr">
         <is>
           <t>liq_ins100</t>
         </is>
       </c>
-      <c r="I20" s="1" t="inlineStr">
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins150</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr">
         <is>
           <t>liq_ins20</t>
         </is>
       </c>
-      <c r="J20" s="1" t="inlineStr">
+      <c r="K21" s="1" t="inlineStr">
         <is>
           <t>liq_ins40</t>
         </is>
       </c>
-      <c r="K20" s="1" t="inlineStr">
+      <c r="L21" s="1" t="inlineStr">
         <is>
           <t>liq_ins60</t>
         </is>
       </c>
-      <c r="L20" s="1" t="inlineStr">
+      <c r="M21" s="1" t="inlineStr">
         <is>
           <t>liq_ins80</t>
         </is>
       </c>
-      <c r="M20" s="1" t="inlineStr">
+      <c r="N21" s="1" t="inlineStr">
         <is>
           <t>liq_noins</t>
         </is>
       </c>
-      <c r="N20" s="1" t="inlineStr">
+      <c r="O21" s="1" t="inlineStr">
         <is>
           <t>noins</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>6"</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>24564.60556014667</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>11132.30645294499</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>14"</t>
+          <t>6"</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>55638.09849680331</v>
+        <v>24564.60556014667</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>0</v>
@@ -9525,8 +10104,8 @@
       <c r="E22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>0</v>
+      <c r="F22" s="3" t="n">
+        <v>11132.30645294499</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>0</v>
@@ -9550,20 +10129,23 @@
         <v>0</v>
       </c>
       <c r="N22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>18"</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>40554.09197233206</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>0</v>
+          <t>14"</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>55638.09849680331</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>0</v>
@@ -9571,11 +10153,11 @@
       <c r="E23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>103186.4576805362</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>40554.09197233206</v>
+      <c r="F23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>0</v>
@@ -9586,8 +10168,8 @@
       <c r="J23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="3" t="n">
-        <v>12956.24980249203</v>
+      <c r="K23" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="L23" s="4" t="n">
         <v>0</v>
@@ -9596,38 +10178,41 @@
         <v>0</v>
       </c>
       <c r="N23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22"</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>0</v>
+          <t>18"</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>40554.09197233206</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="3" t="n">
-        <v>47339.82277666168</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>47339.82277666168</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>103186.4576805362</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>40554.09197233206</v>
       </c>
       <c r="H24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="n">
-        <v>47339.82277666168</v>
+      <c r="I24" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>0</v>
@@ -9635,20 +10220,23 @@
       <c r="K24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="4" t="n">
-        <v>0</v>
+      <c r="L24" s="3" t="n">
+        <v>12956.24980249203</v>
       </c>
       <c r="M24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>26"</t>
+          <t>22"</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
@@ -9658,25 +10246,25 @@
         <v>0</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>256203.7069527653</v>
+        <v>47339.82277666168</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>324741.8647258586</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>171404.5876931935</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>171404.5876931935</v>
+        <v>47339.82277666168</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="3" t="n">
-        <v>68538.15777309323</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>0</v>
+      <c r="I25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>47339.82277666168</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>0</v>
@@ -9688,92 +10276,148 @@
         <v>0</v>
       </c>
       <c r="N25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>26"</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>256203.7069527653</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>324741.8647258586</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>171404.5876931935</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>171404.5876931935</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>68538.15777309323</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>30"</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B27" s="3" t="n">
         <v>98193.82104253241</v>
       </c>
-      <c r="C26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="n">
+      <c r="C27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>98193.82104253241</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>98193.82104253241</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>19459.97994050187</v>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G27" s="3" t="n">
         <v>98193.82104253241</v>
       </c>
-      <c r="H26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="n"/>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="11" t="n"/>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="11" t="n"/>
-      <c r="N29" s="11" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Insulation shell volume = pi * ((r + 0.15m)^2 - r^2) * length, r = nominal pipe diameter / 2 (no pipe-wall-thickness data is modeled, so the nominal diameter is used as the pipe's outer diameter). 0.15 m insulation thickness per user specification.</t>
-        </is>
-      </c>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="11" t="n"/>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="11" t="n"/>
+      <c r="N30" s="11" t="n"/>
+      <c r="O30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Insulation shell volume = pi * ((r + 0.15m)^2 - r^2) * length, r = nominal pipe diameter / 2 (no pipe-wall-thickness data is modeled, so the nominal diameter is used as the pipe's outer diameter). 0.15 m insulation thickness per user specification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Excluded from both tables (older schema, insulation not modeled): bm_dense_2, bm_sco2.</t>
         </is>
@@ -9790,7 +10434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -10104,73 +10748,76 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>bm_dense_2</t>
+          <t>liq_ins150</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>benchmark (dense-phase network)</t>
-        </is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>150</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>bm_sco2</t>
+          <t>bm_dense_2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>benchmark (sCO2 network)</t>
+          <t>benchmark (dense-phase network)</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>noins</t>
+          <t>bm_sco2</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>supercritical</t>
+          <t>benchmark (sCO2 network)</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ins20</t>
+          <t>noins</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -10178,38 +10825,35 @@
           <t>supercritical</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>20</v>
-      </c>
       <c r="D12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="H12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>1041.09</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>401737.3507719593</v>
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ins40</t>
+          <t>ins20</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -10218,7 +10862,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>6</v>
@@ -10236,19 +10880,19 @@
         <v>1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1220.56</v>
+        <v>1041.09</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>470275.5085450526</v>
+        <v>401737.3507719593</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ins60</t>
+          <t>ins40</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -10257,37 +10901,37 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>6</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>932.8499999999999</v>
+        <v>1220.56</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>305183.3317671765</v>
+        <v>470275.5085450526</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ins80</t>
+          <t>ins60</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -10296,37 +10940,37 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>6</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>819.04</v>
+        <v>932.8499999999999</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>310152.500708058</v>
+        <v>305183.3317671765</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ins100</t>
+          <t>ins80</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -10335,7 +10979,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>6</v>
@@ -10353,81 +10997,120 @@
         <v>1</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>370.21</v>
+        <v>819.04</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>138747.9130148645</v>
+        <v>310152.500708058</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>ins100</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>370.21</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>138747.9130148645</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>ins150</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>supercritical</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C18" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D18" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4" t="n">
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4" t="n">
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="J18" s="3" t="n">
         <v>405.9</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K18" s="3" t="n">
         <v>80202.70405694998</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
-      <c r="I20" s="11" t="n"/>
-      <c r="J20" s="11" t="n"/>
-      <c r="K20" s="11" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="11" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Juxtaposes the model's two ways of keeping a pipe above p_min/theta_min: build a booster station, or insulate the pipe so it loses less heat and needs boosting less. Booster reason columns and insulation columns are blank for bm_sco2/bm_dense_2 (older schema -- see the 'Booster reason' and 'Insulation volume' tabs' notes); Total boosters is still shown for them.</t>
         </is>
@@ -10444,7 +11127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -10460,9 +11143,10 @@
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10518,30 +11202,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>liq_ins150</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>liq_ins20</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>liq_ins40</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>liq_ins60</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>liq_ins80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>liq_noins</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>noins</t>
         </is>
@@ -10581,21 +11270,24 @@
         <v>700.6259099927481</v>
       </c>
       <c r="K2" s="3" t="n">
+        <v>753.540610836992</v>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>658.8419295946561</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="M2" s="3" t="n">
         <v>737.7173328301084</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="N2" s="3" t="n">
         <v>725.2013459129305</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="O2" s="3" t="n">
         <v>677.7970576928</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="P2" s="3" t="n">
         <v>672.7545964307138</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="Q2" s="3" t="n">
         <v>1024.471405513181</v>
       </c>
     </row>
@@ -10633,21 +11325,24 @@
         <v>24181.03304</v>
       </c>
       <c r="K3" s="3" t="n">
+        <v>23826.56291</v>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>23723.67947</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="M3" s="3" t="n">
         <v>23586.9629</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="N3" s="3" t="n">
         <v>23826.56291</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="O3" s="3" t="n">
         <v>23597.24004</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="P3" s="3" t="n">
         <v>23774.42934</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="Q3" s="3" t="n">
         <v>23819.94767</v>
       </c>
     </row>
@@ -10685,23 +11380,26 @@
         <v>125.1533903399969</v>
       </c>
       <c r="K4" s="3" t="n">
+        <v>148.9714454999999</v>
+      </c>
+      <c r="L4" s="3" t="n">
         <v>148.9714455</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="M4" s="3" t="n">
         <v>165.1093833399993</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="N4" s="3" t="n">
         <v>148.9714454999999</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="O4" s="3" t="n">
         <v>148.9714454999998</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>148.9714455</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>148.9714455</v>
       </c>
+      <c r="Q4" s="3" t="n">
+        <v>148.9714455</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -10737,21 +11435,24 @@
         <v>2833.698782484014</v>
       </c>
       <c r="K5" s="3" t="n">
+        <v>2437.520456079054</v>
+      </c>
+      <c r="L5" s="3" t="n">
         <v>2494.415789195258</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="M5" s="3" t="n">
         <v>2513.738966388013</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="N5" s="3" t="n">
         <v>2435.149210437197</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="O5" s="3" t="n">
         <v>2629.062778715525</v>
       </c>
-      <c r="O5" s="3" t="n">
+      <c r="P5" s="3" t="n">
         <v>2542.379478390276</v>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="Q5" s="3" t="n">
         <v>3011.776373761153</v>
       </c>
     </row>
@@ -10782,22 +11483,25 @@
       <c r="J6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>96.84114258202197</v>
       </c>
-      <c r="L6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
         <v>30.55414562304001</v>
       </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10835,21 +11539,24 @@
         <v>-30393.76092033066</v>
       </c>
       <c r="K7" s="3" t="n">
+        <v>-30393.76092033071</v>
+      </c>
+      <c r="L7" s="3" t="n">
         <v>-30082.05433903402</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="M7" s="3" t="n">
         <v>-30343.48836729406</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="N7" s="3" t="n">
         <v>-30393.76092033066</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="O7" s="3" t="n">
         <v>-30337.6331618952</v>
       </c>
-      <c r="O7" s="3" t="n">
+      <c r="P7" s="3" t="n">
         <v>-30337.63316189517</v>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="Q7" s="3" t="n">
         <v>-30356.84496999999</v>
       </c>
     </row>
@@ -10887,21 +11594,24 @@
         <v>69634.32908437459</v>
       </c>
       <c r="K8" s="3" t="n">
+        <v>69634.32908437465</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>69406.2238706963</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="M8" s="3" t="n">
         <v>69597.54322262507</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="N8" s="3" t="n">
         <v>69634.32908437471</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="O8" s="3" t="n">
         <v>69593.25880173709</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="P8" s="3" t="n">
         <v>69593.25880173739</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="Q8" s="3" t="n">
         <v>69607.31663000012</v>
       </c>
     </row>
@@ -10939,21 +11649,24 @@
         <v>219.5845808161355</v>
       </c>
       <c r="K9" s="3" t="n">
+        <v>229.3113293539796</v>
+      </c>
+      <c r="L9" s="3" t="n">
         <v>272.448374993706</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>282.6422313599141</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="N9" s="3" t="n">
         <v>229.513737625866</v>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="O9" s="3" t="n">
         <v>238.6839788326142</v>
       </c>
-      <c r="O9" s="3" t="n">
+      <c r="P9" s="3" t="n">
         <v>227.4956853704592</v>
       </c>
-      <c r="P9" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>289.0632183213545</v>
       </c>
     </row>
@@ -10991,21 +11704,24 @@
         <v>10344.95345049647</v>
       </c>
       <c r="K10" s="3" t="n">
+        <v>10344.95345049648</v>
+      </c>
+      <c r="L10" s="3" t="n">
         <v>10311.06957449206</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="M10" s="3" t="n">
         <v>10339.48878898885</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="N10" s="3" t="n">
         <v>10344.95345049649</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="O10" s="3" t="n">
         <v>10338.85232408643</v>
       </c>
-      <c r="O10" s="3" t="n">
+      <c r="P10" s="3" t="n">
         <v>10338.85232408647</v>
       </c>
-      <c r="P10" s="3" t="n">
+      <c r="Q10" s="3" t="n">
         <v>10340.94066100002</v>
       </c>
     </row>
@@ -11043,21 +11759,24 @@
         <v>4060.949479999987</v>
       </c>
       <c r="K11" s="3" t="n">
+        <v>4060.94948</v>
+      </c>
+      <c r="L11" s="3" t="n">
         <v>4060.949479999995</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="M11" s="3" t="n">
         <v>4060.949479999986</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="N11" s="3" t="n">
         <v>4060.949480000001</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="O11" s="3" t="n">
         <v>4060.949479999972</v>
       </c>
-      <c r="O11" s="3" t="n">
+      <c r="P11" s="3" t="n">
         <v>4060.949479999988</v>
       </c>
-      <c r="P11" s="3" t="n">
+      <c r="Q11" s="3" t="n">
         <v>4060.94948</v>
       </c>
     </row>
@@ -11095,21 +11814,24 @@
         <v>30.30629113715363</v>
       </c>
       <c r="K12" s="3" t="n">
+        <v>35.21407371456303</v>
+      </c>
+      <c r="L12" s="3" t="n">
         <v>31.55427013540906</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="M12" s="3" t="n">
         <v>36.07693037235904</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="N12" s="3" t="n">
         <v>34.48622183996001</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="O12" s="3" t="n">
         <v>29.71996601594519</v>
       </c>
-      <c r="O12" s="3" t="n">
+      <c r="P12" s="3" t="n">
         <v>26.62594335186155</v>
       </c>
-      <c r="P12" s="3" t="n">
+      <c r="Q12" s="3" t="n">
         <v>44.94061397611854</v>
       </c>
     </row>
@@ -11147,21 +11869,24 @@
         <v>1652.22359</v>
       </c>
       <c r="K13" s="3" t="n">
+        <v>1612.66696</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>1601.18934</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="M13" s="3" t="n">
         <v>1585.91461</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="N13" s="3" t="n">
         <v>1612.66696</v>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="O13" s="3" t="n">
         <v>1587.06575</v>
       </c>
-      <c r="O13" s="3" t="n">
+      <c r="P13" s="3" t="n">
         <v>1606.84595</v>
       </c>
-      <c r="P13" s="3" t="n">
+      <c r="Q13" s="3" t="n">
         <v>1611.9264</v>
       </c>
     </row>
@@ -11202,10 +11927,10 @@
         <v>46.97010415</v>
       </c>
       <c r="L14" s="3" t="n">
+        <v>46.97010415</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>55.63934095</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>46.97010415</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>46.97010415</v>
@@ -11216,6 +11941,9 @@
       <c r="P14" s="3" t="n">
         <v>46.97010415</v>
       </c>
+      <c r="Q14" s="3" t="n">
+        <v>46.97010415</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -11251,21 +11979,24 @@
         <v>810.9191663411908</v>
       </c>
       <c r="K15" s="3" t="n">
+        <v>684.334896417256</v>
+      </c>
+      <c r="L15" s="3" t="n">
         <v>723.82196580907</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="M15" s="3" t="n">
         <v>741.587808809696</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="N15" s="3" t="n">
         <v>682.981213044024</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="O15" s="3" t="n">
         <v>778.450136475152</v>
       </c>
-      <c r="O15" s="3" t="n">
+      <c r="P15" s="3" t="n">
         <v>735.50880075495</v>
       </c>
-      <c r="P15" s="3" t="n">
+      <c r="Q15" s="3" t="n">
         <v>808.7254270931439</v>
       </c>
     </row>
@@ -11296,22 +12027,25 @@
       <c r="J16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="n">
         <v>39.00446648804999</v>
       </c>
-      <c r="L16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="n">
         <v>12.306343296</v>
       </c>
-      <c r="N16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11349,21 +12083,24 @@
         <v>92479.20196745897</v>
       </c>
       <c r="K17" s="3" t="n">
+        <v>92479.20196745859</v>
+      </c>
+      <c r="L17" s="3" t="n">
         <v>93080.28297062905</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="M17" s="3" t="n">
         <v>92623.05028771974</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="N17" s="3" t="n">
         <v>92479.20196745871</v>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="O17" s="3" t="n">
         <v>92639.80419040704</v>
       </c>
-      <c r="O17" s="3" t="n">
+      <c r="P17" s="3" t="n">
         <v>92639.8041904069</v>
       </c>
-      <c r="P17" s="3" t="n">
+      <c r="Q17" s="3" t="n">
         <v>92584.83212000001</v>
       </c>
     </row>
@@ -11416,6 +12153,9 @@
         <v>0</v>
       </c>
       <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11430,7 +12170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -11443,12 +12183,13 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11504,30 +12245,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>liq_ins150</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>liq_ins20</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>liq_ins40</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>liq_ins60</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>liq_ins80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>liq_noins</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>noins</t>
         </is>
@@ -11567,21 +12313,24 @@
         <v>4.060949479999987</v>
       </c>
       <c r="K2" s="3" t="n">
+        <v>4.060949480000001</v>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>4.060949479999995</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="M2" s="3" t="n">
         <v>4.060949479999986</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="N2" s="3" t="n">
         <v>4.060949480000001</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="O2" s="3" t="n">
         <v>4.060949479999972</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="P2" s="3" t="n">
         <v>4.060949479999988</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="Q2" s="3" t="n">
         <v>4.060949480000001</v>
       </c>
     </row>
@@ -11636,6 +12385,9 @@
       <c r="P3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="Q3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -11671,21 +12423,24 @@
         <v>2.958852172824011</v>
       </c>
       <c r="K4" s="3" t="n">
+        <v>2.586491901579054</v>
+      </c>
+      <c r="L4" s="3" t="n">
         <v>2.643387234695258</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="M4" s="3" t="n">
         <v>2.678848349728012</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="N4" s="3" t="n">
         <v>2.584120655937197</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="O4" s="3" t="n">
         <v>2.778034224215525</v>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="P4" s="3" t="n">
         <v>2.691350923890276</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="Q4" s="3" t="n">
         <v>3.160747819261153</v>
       </c>
     </row>
@@ -11723,21 +12478,24 @@
         <v>0.8450942560911908</v>
       </c>
       <c r="K5" s="3" t="n">
+        <v>0.731305000567256</v>
+      </c>
+      <c r="L5" s="3" t="n">
         <v>0.77079206995907</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="M5" s="3" t="n">
         <v>0.797227149759696</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="N5" s="3" t="n">
         <v>0.729951317194024</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="O5" s="3" t="n">
         <v>0.8254202406251521</v>
       </c>
-      <c r="O5" s="3" t="n">
+      <c r="P5" s="3" t="n">
         <v>0.78247890490495</v>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="Q5" s="3" t="n">
         <v>0.8556955312431439</v>
       </c>
     </row>
@@ -11774,22 +12532,25 @@
       <c r="J6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>0.09684114258202198</v>
       </c>
-      <c r="L6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
         <v>0.03055414562304001</v>
       </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11826,22 +12587,25 @@
       <c r="J7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
         <v>0.03900446648804999</v>
       </c>
-      <c r="L7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
         <v>0.012306343296</v>
       </c>
-      <c r="N7" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11879,21 +12643,24 @@
         <v>24.88165894999275</v>
       </c>
       <c r="K8" s="3" t="n">
+        <v>24.58010352083699</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>24.38252139959465</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="M8" s="3" t="n">
         <v>24.3246802328301</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="N8" s="3" t="n">
         <v>24.55176425591293</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="O8" s="3" t="n">
         <v>24.2750370976928</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="P8" s="3" t="n">
         <v>24.44718393643071</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="Q8" s="3" t="n">
         <v>24.84441907551318</v>
       </c>
     </row>
@@ -11931,21 +12698,24 @@
         <v>1.682529881137154</v>
       </c>
       <c r="K9" s="3" t="n">
+        <v>1.647881033714563</v>
+      </c>
+      <c r="L9" s="3" t="n">
         <v>1.632743610135409</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>1.621991540372359</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="N9" s="3" t="n">
         <v>1.64715318183996</v>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="O9" s="3" t="n">
         <v>1.616785716015945</v>
       </c>
-      <c r="O9" s="3" t="n">
+      <c r="P9" s="3" t="n">
         <v>1.633471893351861</v>
       </c>
-      <c r="P9" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>1.656867013976119</v>
       </c>
     </row>
@@ -11983,21 +12753,24 @@
         <v>10.56453803131261</v>
       </c>
       <c r="K10" s="3" t="n">
+        <v>10.57426477985046</v>
+      </c>
+      <c r="L10" s="3" t="n">
         <v>10.58351794948577</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="M10" s="3" t="n">
         <v>10.62213102034876</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="N10" s="3" t="n">
         <v>10.57446718812236</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="O10" s="3" t="n">
         <v>10.57753630291904</v>
       </c>
-      <c r="O10" s="3" t="n">
+      <c r="P10" s="3" t="n">
         <v>10.56634800945693</v>
       </c>
-      <c r="P10" s="3" t="n">
+      <c r="Q10" s="3" t="n">
         <v>10.63000387932138</v>
       </c>
     </row>
@@ -12035,21 +12808,24 @@
         <v>44.99362277135769</v>
       </c>
       <c r="K11" s="6" t="n">
+        <v>44.18099571654832</v>
+      </c>
+      <c r="L11" s="6" t="n">
         <v>44.07391174387015</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="6" t="n">
         <v>44.10582777303892</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="N11" s="6" t="n">
         <v>44.14840607900646</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="6" t="n">
         <v>44.13376306146843</v>
       </c>
-      <c r="O11" s="6" t="n">
+      <c r="P11" s="6" t="n">
         <v>44.18178314803472</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="6" t="n">
         <v>45.20868279931497</v>
       </c>
     </row>
@@ -12087,21 +12863,24 @@
         <v>-30.39376092033066</v>
       </c>
       <c r="K12" s="3" t="n">
+        <v>-30.39376092033071</v>
+      </c>
+      <c r="L12" s="3" t="n">
         <v>-30.08205433903402</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="M12" s="3" t="n">
         <v>-30.34348836729406</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="N12" s="3" t="n">
         <v>-30.39376092033066</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="O12" s="3" t="n">
         <v>-30.3376331618952</v>
       </c>
-      <c r="O12" s="3" t="n">
+      <c r="P12" s="3" t="n">
         <v>-30.33763316189517</v>
       </c>
-      <c r="P12" s="3" t="n">
+      <c r="Q12" s="3" t="n">
         <v>-30.35684496999999</v>
       </c>
     </row>
@@ -12139,21 +12918,24 @@
         <v>14.59986185102703</v>
       </c>
       <c r="K13" s="6" t="n">
+        <v>13.78723479621761</v>
+      </c>
+      <c r="L13" s="6" t="n">
         <v>13.99185740483613</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="6" t="n">
         <v>13.76233940574486</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="N13" s="6" t="n">
         <v>13.7546451586758</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="6" t="n">
         <v>13.79612989957323</v>
       </c>
-      <c r="O13" s="6" t="n">
+      <c r="P13" s="6" t="n">
         <v>13.84414998613955</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="6" t="n">
         <v>14.85183782931498</v>
       </c>
     </row>
@@ -12191,21 +12973,24 @@
         <v>69.6343290843746</v>
       </c>
       <c r="K14" s="3" t="n">
+        <v>69.63432908437466</v>
+      </c>
+      <c r="L14" s="3" t="n">
         <v>69.40622387069629</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="M14" s="3" t="n">
         <v>69.59754322262508</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="N14" s="3" t="n">
         <v>69.63432908437471</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="O14" s="3" t="n">
         <v>69.59325880173709</v>
       </c>
-      <c r="O14" s="3" t="n">
+      <c r="P14" s="3" t="n">
         <v>69.59325880173739</v>
       </c>
-      <c r="P14" s="3" t="n">
+      <c r="Q14" s="3" t="n">
         <v>69.60731663000011</v>
       </c>
     </row>
@@ -12243,21 +13028,24 @@
         <v>92.47920196745896</v>
       </c>
       <c r="K15" s="3" t="n">
+        <v>92.47920196745859</v>
+      </c>
+      <c r="L15" s="3" t="n">
         <v>93.08028297062906</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="M15" s="3" t="n">
         <v>92.62305028771975</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="N15" s="3" t="n">
         <v>92.47920196745871</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="O15" s="3" t="n">
         <v>92.63980419040705</v>
       </c>
-      <c r="O15" s="3" t="n">
+      <c r="P15" s="3" t="n">
         <v>92.63980419040689</v>
       </c>
-      <c r="P15" s="3" t="n">
+      <c r="Q15" s="3" t="n">
         <v>92.58483212</v>
       </c>
     </row>
@@ -12272,7 +13060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12506,102 +13294,102 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>liq_ins20</t>
+          <t>liq_ins150</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>321.2</v>
+        <v>180.83</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>526.2199999999999</v>
+        <v>546.47</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1103.85</v>
+        <v>1065.85</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1875.18</v>
+        <v>1978.91</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2422.78</v>
+        <v>2495.26</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>liq_ins40</t>
+          <t>liq_ins20</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>221.96</v>
+        <v>321.2</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>885.0799999999999</v>
+        <v>526.2199999999999</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1358.93</v>
+        <v>1103.85</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1649.83</v>
+        <v>1875.18</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2394.66</v>
+        <v>2422.78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>liq_ins60</t>
+          <t>liq_ins40</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>203.63</v>
+        <v>221.96</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>491.15</v>
+        <v>885.0799999999999</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1010.53</v>
+        <v>1358.93</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1923.59</v>
+        <v>1649.83</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2540.54</v>
+        <v>2394.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>liq_ins80</t>
+          <t>liq_ins60</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>280.07</v>
+        <v>203.63</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>765.3900000000001</v>
+        <v>491.15</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1056.2</v>
+        <v>1010.53</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1827.53</v>
+        <v>1923.59</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>2445.26</v>
+        <v>2540.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>liq_noins</t>
+          <t>liq_ins80</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
         <v>280.07</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>565.3199999999999</v>
+        <v>765.3900000000001</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>1056.2</v>
@@ -12616,22 +13404,44 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>liq_noins</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>280.07</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>565.3199999999999</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1056.2</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1827.53</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>2445.26</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>noins</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B17" s="3" t="n">
         <v>321.2</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C17" s="3" t="n">
         <v>526.2199999999999</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>1080.45</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>2041.44</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>3297.03</v>
       </c>
     </row>
@@ -12646,7 +13456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12662,9 +13472,10 @@
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12727,30 +13538,35 @@
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
+          <t>liq_ins150</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
           <t>liq_ins20</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>liq_ins40</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>liq_ins60</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>liq_ins80</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>liq_noins</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>noins</t>
         </is>
@@ -12796,15 +13612,18 @@
         <v>0</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="P3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12859,6 +13678,9 @@
       <c r="P4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="Q4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -12911,6 +13733,9 @@
       <c r="P5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="Q5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -12946,21 +13771,24 @@
         <v>0</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12998,21 +13826,24 @@
         <v>2</v>
       </c>
       <c r="K7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L7" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="M7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O7" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="P7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13050,16 +13881,16 @@
         <v>4</v>
       </c>
       <c r="K8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>3</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>2</v>
@@ -13067,6 +13898,9 @@
       <c r="P8" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="Q8" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -13117,6 +13951,9 @@
         <v>3</v>
       </c>
       <c r="P9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="4" t="n">
         <v>5</v>
       </c>
     </row>
@@ -13163,12 +14000,15 @@
         <v>2</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>3</v>
       </c>
       <c r="P10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13206,21 +14046,24 @@
         <v>3</v>
       </c>
       <c r="K11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>3</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O11" s="4" t="n">
         <v>2</v>
       </c>
       <c r="P11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13267,12 +14110,15 @@
         <v>2</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O12" s="4" t="n">
         <v>3</v>
       </c>
       <c r="P12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13337,30 +14183,35 @@
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
+          <t>liq_ins150</t>
+        </is>
+      </c>
+      <c r="L15" s="1" t="inlineStr">
+        <is>
           <t>liq_ins20</t>
         </is>
       </c>
-      <c r="L15" s="1" t="inlineStr">
+      <c r="M15" s="1" t="inlineStr">
         <is>
           <t>liq_ins40</t>
         </is>
       </c>
-      <c r="M15" s="1" t="inlineStr">
+      <c r="N15" s="1" t="inlineStr">
         <is>
           <t>liq_ins60</t>
         </is>
       </c>
-      <c r="N15" s="1" t="inlineStr">
+      <c r="O15" s="1" t="inlineStr">
         <is>
           <t>liq_ins80</t>
         </is>
       </c>
-      <c r="O15" s="1" t="inlineStr">
+      <c r="P15" s="1" t="inlineStr">
         <is>
           <t>liq_noins</t>
         </is>
       </c>
-      <c r="P15" s="1" t="inlineStr">
+      <c r="Q15" s="1" t="inlineStr">
         <is>
           <t>noins</t>
         </is>
@@ -13405,16 +14256,19 @@
       <c r="L16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="n">
         <v>100.6</v>
       </c>
-      <c r="N16" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="3" t="n">
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3" t="n">
         <v>453.5700000000001</v>
       </c>
     </row>
@@ -13469,6 +14323,9 @@
       <c r="P17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="Q17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -13521,6 +14378,9 @@
       <c r="P18" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="Q18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -13555,22 +14415,25 @@
       <c r="J19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="n">
+      <c r="K19" s="3" t="n">
+        <v>178.72</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3" t="n">
         <v>78.12</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="N19" s="3" t="n">
         <v>123.4</v>
       </c>
-      <c r="N19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="3" t="n">
+      <c r="O19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="n">
         <v>100.6</v>
       </c>
-      <c r="P19" s="3" t="n">
+      <c r="Q19" s="3" t="n">
         <v>141.73</v>
       </c>
     </row>
@@ -13608,21 +14471,24 @@
         <v>219.85</v>
       </c>
       <c r="K20" s="3" t="n">
+        <v>141.73</v>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>219.85</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>141.73</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>141.73</v>
       </c>
       <c r="N20" s="3" t="n">
+        <v>141.73</v>
+      </c>
+      <c r="O20" s="3" t="n">
         <v>242.33</v>
       </c>
-      <c r="O20" s="3" t="n">
+      <c r="P20" s="3" t="n">
         <v>141.73</v>
       </c>
-      <c r="P20" s="4" t="n">
+      <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13660,21 +14526,24 @@
         <v>843.26</v>
       </c>
       <c r="K21" s="3" t="n">
+        <v>716.16</v>
+      </c>
+      <c r="L21" s="3" t="n">
         <v>895.63</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>716.16</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>716.16</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>670.88</v>
+        <v>716.16</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>670.88</v>
       </c>
       <c r="P21" s="3" t="n">
+        <v>670.88</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>462.48</v>
       </c>
     </row>
@@ -13727,6 +14596,9 @@
         <v>435.81</v>
       </c>
       <c r="P22" s="3" t="n">
+        <v>435.81</v>
+      </c>
+      <c r="Q22" s="3" t="n">
         <v>750.96</v>
       </c>
     </row>
@@ -13773,12 +14645,15 @@
         <v>412.8200000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>458.1</v>
+        <v>412.8200000000001</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>458.1</v>
       </c>
       <c r="P23" s="3" t="n">
+        <v>458.1</v>
+      </c>
+      <c r="Q23" s="3" t="n">
         <v>401.3200000000001</v>
       </c>
     </row>
@@ -13816,21 +14691,24 @@
         <v>473.85</v>
       </c>
       <c r="K24" s="3" t="n">
+        <v>473.85</v>
+      </c>
+      <c r="L24" s="3" t="n">
         <v>322.5</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>473.85</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>473.85</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>322.5</v>
+        <v>473.85</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>322.5</v>
       </c>
       <c r="P24" s="3" t="n">
+        <v>322.5</v>
+      </c>
+      <c r="Q24" s="3" t="n">
         <v>501.97</v>
       </c>
     </row>
@@ -13877,12 +14755,15 @@
         <v>136.17</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>315.64</v>
+        <v>136.17</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>315.64</v>
       </c>
-      <c r="P25" s="4" t="n">
+      <c r="P25" s="3" t="n">
+        <v>315.64</v>
+      </c>
+      <c r="Q25" s="4" t="n">
         <v>585</v>
       </c>
     </row>
@@ -13897,7 +14778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14132,88 +15013,91 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>bm_dense_2</t>
+          <t>liq_ins150</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>benchmark (dense-phase network)</t>
-        </is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>150</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>13.72668578832562</v>
+        <v>13.78723479621761</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2445.26</v>
+        <v>2495.26</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1192.365999999997</v>
+        <v>1192.366</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>5613.589470373548</v>
+        <v>5525.370020045052</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>11.51214122872143</v>
+        <v>11.56292178426558</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>bm_sco2</t>
+          <t>bm_dense_2</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>benchmark (sCO2 network)</t>
+          <t>benchmark (dense-phase network)</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>13.96324914365908</v>
+        <v>13.72668578832562</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2997.59</v>
+        <v>2445.26</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>1192.365999999997</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>4658.158435162608</v>
+        <v>5613.589470373548</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>11.71053950184685</v>
+        <v>11.51214122872143</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>noins</t>
+          <t>bm_sco2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>supercritical</t>
+          <t>benchmark (sCO2 network)</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>14.85183782931498</v>
+        <v>13.96324914365908</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>3297.03</v>
+        <v>2997.59</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1192.366</v>
+        <v>1192.365999999997</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>4504.611067935378</v>
+        <v>4658.158435162608</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>12.45577098752815</v>
+        <v>11.71053950184685</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ins20</t>
+          <t>noins</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -14221,29 +15105,26 @@
           <t>supercritical</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>20</v>
-      </c>
       <c r="D11" s="3" t="n">
-        <v>14.02511458813818</v>
+        <v>14.85183782931498</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2394.66</v>
+        <v>3297.03</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1192.366000000001</v>
+        <v>1192.366</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>5856.829190005337</v>
+        <v>4504.611067935378</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>11.7624241115045</v>
+        <v>12.45577098752815</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ins40</t>
+          <t>ins20</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -14252,28 +15133,28 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>14.52751772781437</v>
+        <v>14.02511458813818</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2574.13</v>
+        <v>2394.66</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>1192.366000000001</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>5643.661247805809</v>
+        <v>5856.829190005337</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>12.18377388135384</v>
+        <v>11.7624241115045</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ins60</t>
+          <t>ins40</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -14282,28 +15163,28 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>14.02141706218577</v>
+        <v>14.52751772781437</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>3035.1</v>
+        <v>2574.13</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1192.365999999995</v>
+        <v>1192.366000000001</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>4619.754559054322</v>
+        <v>5643.661247805809</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>11.75932311235462</v>
+        <v>12.18377388135384</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ins80</t>
+          <t>ins60</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -14312,28 +15193,28 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>14.5180377170776</v>
+        <v>14.02141706218577</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2560.89</v>
+        <v>3035.1</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1192.365999999997</v>
+        <v>1192.365999999995</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>5669.137572124378</v>
+        <v>4619.754559054322</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>12.17582329341631</v>
+        <v>11.75932311235462</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ins100</t>
+          <t>ins80</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -14342,28 +15223,28 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>14.57670902698809</v>
+        <v>14.5180377170776</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2659.17</v>
+        <v>2560.89</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1192.365999999999</v>
+        <v>1192.365999999997</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>5481.676247471236</v>
+        <v>5669.137572124378</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>12.22502908250328</v>
+        <v>12.17582329341631</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ins150</t>
+          <t>ins100</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -14372,21 +15253,51 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.99495176761194</v>
+        <v>14.57670902698809</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3311.17</v>
+        <v>2659.17</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>1192.365999999999</v>
       </c>
       <c r="G16" s="3" t="n">
+        <v>5481.676247471236</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>12.22502908250328</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ins150</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>supercritical</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>14.99495176761194</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>3311.17</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>1192.365999999999</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>4528.596166192598</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H17" s="3" t="n">
         <v>12.57579616293316</v>
       </c>
     </row>
@@ -15331,7 +16242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -15342,6 +16253,7 @@
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15392,6 +16304,11 @@
           <t>liq_ins100</t>
         </is>
       </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins150</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -15420,6 +16337,9 @@
       <c r="H3" s="3" t="n">
         <v>4.060949479999987</v>
       </c>
+      <c r="I3" s="3" t="n">
+        <v>4.060949480000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -15448,6 +16368,9 @@
       <c r="H4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="I4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -15476,6 +16399,9 @@
       <c r="H5" s="3" t="n">
         <v>2.958852172824011</v>
       </c>
+      <c r="I5" s="3" t="n">
+        <v>2.586491901579054</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -15504,6 +16430,9 @@
       <c r="H6" s="3" t="n">
         <v>0.8450942560911908</v>
       </c>
+      <c r="I6" s="3" t="n">
+        <v>0.731305000567256</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -15532,6 +16461,9 @@
       <c r="H7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="I7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -15560,6 +16492,9 @@
       <c r="H8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -15588,6 +16523,9 @@
       <c r="H9" s="3" t="n">
         <v>24.88165894999275</v>
       </c>
+      <c r="I9" s="3" t="n">
+        <v>24.58010352083699</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -15616,6 +16554,9 @@
       <c r="H10" s="3" t="n">
         <v>1.682529881137154</v>
       </c>
+      <c r="I10" s="3" t="n">
+        <v>1.647881033714563</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -15644,6 +16585,9 @@
       <c r="H11" s="3" t="n">
         <v>10.56453803131261</v>
       </c>
+      <c r="I11" s="3" t="n">
+        <v>10.57426477985046</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -15672,6 +16616,9 @@
       <c r="H12" s="6" t="n">
         <v>44.99362277135769</v>
       </c>
+      <c r="I12" s="6" t="n">
+        <v>44.18099571654832</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -15700,6 +16647,9 @@
       <c r="H13" s="3" t="n">
         <v>-30.39376092033066</v>
       </c>
+      <c r="I13" s="3" t="n">
+        <v>-30.39376092033071</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -15728,6 +16678,9 @@
       <c r="H14" s="6" t="n">
         <v>14.59986185102703</v>
       </c>
+      <c r="I14" s="6" t="n">
+        <v>13.78723479621761</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -15756,6 +16709,9 @@
       <c r="H15" s="3" t="n">
         <v>69.6343290843746</v>
       </c>
+      <c r="I15" s="3" t="n">
+        <v>69.63432908437466</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -15783,6 +16739,9 @@
       </c>
       <c r="H16" s="3" t="n">
         <v>92.47920196745896</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>92.47920196745859</v>
       </c>
     </row>
     <row r="17"/>
@@ -15834,6 +16793,11 @@
           <t>liq_ins100</t>
         </is>
       </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>liq_ins150</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -15862,6 +16826,9 @@
       <c r="H20" s="9" t="n">
         <v>2.187120091186478e-14</v>
       </c>
+      <c r="I20" s="9" t="n">
+        <v>3.499392145898365e-13</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -15897,6 +16864,9 @@
       <c r="H22" s="9" t="n">
         <v>12.18200398591513</v>
       </c>
+      <c r="I22" s="9" t="n">
+        <v>-1.935673746233874</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -15925,6 +16895,9 @@
       <c r="H23" s="9" t="n">
         <v>11.07850123921933</v>
       </c>
+      <c r="I23" s="9" t="n">
+        <v>-3.877865899266292</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -15967,6 +16940,9 @@
       <c r="H26" s="9" t="n">
         <v>1.91009999208932</v>
       </c>
+      <c r="I26" s="9" t="n">
+        <v>0.6749916739428183</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -15995,6 +16971,9 @@
       <c r="H27" s="9" t="n">
         <v>3.054955297387997</v>
       </c>
+      <c r="I27" s="9" t="n">
+        <v>0.9327133911534431</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -16023,6 +17002,9 @@
       <c r="H28" s="9" t="n">
         <v>0.07083595725556349</v>
       </c>
+      <c r="I28" s="9" t="n">
+        <v>0.1629709710577711</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -16051,6 +17033,9 @@
       <c r="H29" s="10" t="n">
         <v>2.108971256736409</v>
       </c>
+      <c r="I29" s="10" t="n">
+        <v>0.2647874042017083</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -16079,6 +17064,9 @@
       <c r="H30" s="9" t="n">
         <v>0.1850103405756335</v>
       </c>
+      <c r="I30" s="9" t="n">
+        <v>0.1850103405757975</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -16107,6 +17095,9 @@
       <c r="H31" s="10" t="n">
         <v>6.361157209878218</v>
       </c>
+      <c r="I31" s="10" t="n">
+        <v>0.4411043483161026</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -16135,6 +17126,9 @@
       <c r="H32" s="9" t="n">
         <v>0.0590147427270793</v>
       </c>
+      <c r="I32" s="9" t="n">
+        <v>0.05901474272716099</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -16162,6 +17156,9 @@
       </c>
       <c r="H33" s="9" t="n">
         <v>-0.1733620060526287</v>
+      </c>
+      <c r="I33" s="9" t="n">
+        <v>-0.1733620060530275</v>
       </c>
     </row>
   </sheetData>
